--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B01_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B01_Normal_2.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1865502853357017</v>
+        <v>0.1865600545781031</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9027069616915873</v>
+        <v>0.9025130183448353</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329790079151363</v>
+        <v>1.329840539349983</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.333486823954726</v>
+        <v>5.331086360382172</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.042760034830393</v>
+        <v>6.039954809969425</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.774211633003286</v>
+        <v>9.635797748144768</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47404150664014</v>
+        <v>10.47449632497913</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>10.50943319366649</v>
+        <v>10.50475136658863</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33737930054762</v>
+        <v>12.33786735892068</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.112358201660258</v>
+        <v>1.112431640076021</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.062777698332418</v>
+        <v>1.063099514135826</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5772589909199825</v>
+        <v>0.5792498871576799</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>15.92122532206255</v>
+        <v>16.08614487448754</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>15.92244207042752</v>
+        <v>15.9224055805709</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>15.95062527901377</v>
+        <v>15.94907264007682</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>16.68125211750191</v>
+        <v>16.68150359318814</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>17.13662195006867</v>
+        <v>17.13699864778113</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>17.65643758803501</v>
+        <v>17.65606000717672</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>17.726221843046</v>
+        <v>17.72686803633449</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>17.81936612530993</v>
+        <v>17.81944109171629</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83069852722052</v>
+        <v>17.82989940170764</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.91045501285387</v>
+        <v>17.91105143658421</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>18.11075800455528</v>
+        <v>18.11063187715624</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>18.25333437977661</v>
+        <v>18.25347872265014</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>18.31313623191253</v>
+        <v>18.31300880162258</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19251281614148</v>
+        <v>18.18374248726346</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>18.43101520147438</v>
+        <v>18.43115021407112</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>18.5685952563802</v>
+        <v>18.56838849707095</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.58008141167307</v>
+        <v>18.58191783635835</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.83955821569582</v>
+        <v>18.84045488162381</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>18.7683839298948</v>
+        <v>18.76887581351305</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>18.73776743207468</v>
+        <v>18.74229667334115</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>18.54743048859889</v>
+        <v>18.54653760366034</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>18.15252804766378</v>
+        <v>18.15454817016082</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18.08003792003841</v>
+        <v>18.08007013293001</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>18.0508829171354</v>
+        <v>18.04915627873921</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.7490806393877</v>
+        <v>17.74861576103778</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>17.81814662802715</v>
+        <v>17.79881074691802</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99225470919088</v>
+        <v>17.97859383075771</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>18.04864477364506</v>
+        <v>18.04209307204975</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>18.06393349092241</v>
+        <v>18.05583693465113</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>18.26553935250956</v>
+        <v>18.26535630570529</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25615665036968</v>
+        <v>18.25543714052691</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>18.32865305918012</v>
+        <v>18.35082486847733</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>18.22115293721825</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>18.30135144683257</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>18.56867116826499</v>
+        <v>18.62276903281257</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>19.21730918670944</v>
+        <v>19.36546901145579</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.93538345298557</v>
+        <v>19.89377638396549</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>19.93538345298557</v>
+        <v>19.89377638396549</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>20.00981556112236</v>
+        <v>19.95730210915573</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>5</v>
       </c>
       <c r="K72" t="n">
-        <v>20.00981556112236</v>
+        <v>19.95730210915573</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>21.13985137760104</v>
+        <v>21.00429376107303</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>5</v>
       </c>
       <c r="K74" t="n">
-        <v>21.25752534241971</v>
+        <v>21.19153026999809</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>21.24478764721551</v>
+        <v>21.20271511536878</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>21.24478764721551</v>
+        <v>21.20271511536878</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>20.91401769073484</v>
+        <v>0.6098121915157551</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>21.75249733392203</v>
+        <v>22.81637576394737</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>18.31538578099143</v>
+        <v>22.45144185382393</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>18.31538578099143</v>
+        <v>22.45144185382393</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>41.15307330033042</v>
+        <v>0.8260418668445116</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>55.6368087571851</v>
+        <v>56.23003942877807</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>6</v>
       </c>
       <c r="K83" t="n">
-        <v>42.99916497611289</v>
+        <v>45.66360168374498</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>40.56424938189363</v>
+        <v>40.59325963239543</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>33.49840842426605</v>
+        <v>33.47802446979679</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="K86" t="n">
-        <v>23.51115280153341</v>
+        <v>23.49332569301106</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>23.07759859367414</v>
+        <v>23.23111356074586</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>6</v>
       </c>
       <c r="K88" t="n">
-        <v>23.03288491493475</v>
+        <v>23.01582633742614</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>22.66480968815676</v>
+        <v>26.24216908963513</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>22.62487457301624</v>
+        <v>24.43540424109552</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>22.35957699356508</v>
+        <v>22.3884218643085</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>22.35957699356508</v>
+        <v>22.3884218643085</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>6</v>
       </c>
       <c r="K93" t="n">
-        <v>22.4810658565194</v>
+        <v>22.44510803430239</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>6</v>
       </c>
       <c r="K94" t="n">
-        <v>23.00388300949592</v>
+        <v>22.49401812226683</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>22.60724382801739</v>
+        <v>22.49694087128349</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>6</v>
       </c>
       <c r="K96" t="n">
-        <v>22.41499665150971</v>
+        <v>22.19039193738289</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>21.77700237518826</v>
+        <v>21.76284238497333</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>6</v>
       </c>
       <c r="K98" t="n">
-        <v>21.77700237518826</v>
+        <v>21.76284238497333</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>25.95407996901959</v>
+        <v>21.65492269454226</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>20.6651522369616</v>
+        <v>20.57281945073719</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>20.58203948620306</v>
+        <v>20.50179656936968</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>6</v>
       </c>
       <c r="K102" t="n">
-        <v>20.05324427496122</v>
+        <v>20.1367742844572</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>6</v>
       </c>
       <c r="K103" t="n">
-        <v>20.05324427496122</v>
+        <v>20.1367742844572</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>6</v>
       </c>
       <c r="K104" t="n">
-        <v>10.13286816744238</v>
+        <v>10.05556289128236</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>10.13286816744238</v>
+        <v>10.05556289128236</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>9.313454523502497</v>
+        <v>9.249788548710319</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>9.313454523502497</v>
+        <v>9.249788548710319</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>6</v>
       </c>
       <c r="K108" t="n">
-        <v>9.006605764587595</v>
+        <v>9.001199936508684</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>8.855391791179059</v>
+        <v>8.859202453554882</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>8.978645588225934</v>
+        <v>8.984742925862029</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>6</v>
       </c>
       <c r="K111" t="n">
-        <v>8.984199379338564</v>
+        <v>8.988563827679902</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>6</v>
       </c>
       <c r="K112" t="n">
-        <v>9.061980501635373</v>
+        <v>9.057072937995757</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>6</v>
       </c>
       <c r="K113" t="n">
-        <v>9.061980501635373</v>
+        <v>9.057072937995757</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>6</v>
       </c>
       <c r="K114" t="n">
-        <v>9.044872040221554</v>
+        <v>9.045523308623421</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>6</v>
       </c>
       <c r="K115" t="n">
-        <v>8.817828618037916</v>
+        <v>8.809891251011997</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>6</v>
       </c>
       <c r="K116" t="n">
-        <v>8.013828136438326</v>
+        <v>8.01349959414503</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>7.881424971903225</v>
+        <v>7.879726061462629</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>6</v>
       </c>
       <c r="K118" t="n">
-        <v>7.614794171987974</v>
+        <v>7.613353376700388</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>6</v>
       </c>
       <c r="K119" t="n">
-        <v>7.614794171987974</v>
+        <v>7.613353376700388</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>6</v>
       </c>
       <c r="K120" t="n">
-        <v>7.525888632454506</v>
+        <v>7.52583147660655</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>6</v>
       </c>
       <c r="K121" t="n">
-        <v>7.648109426969325</v>
+        <v>7.649937527108574</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>7.833439394377753</v>
+        <v>7.834451497123795</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>6</v>
       </c>
       <c r="K123" t="n">
-        <v>7.877726027147521</v>
+        <v>7.878513743038085</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>6</v>
       </c>
       <c r="K124" t="n">
-        <v>7.996504394876585</v>
+        <v>7.996384831667157</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>6</v>
       </c>
       <c r="K125" t="n">
-        <v>8.026213232574577</v>
+        <v>8.026924327986121</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>6</v>
       </c>
       <c r="K126" t="n">
-        <v>8.026213232574577</v>
+        <v>8.026924327986121</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>8.218318514120106</v>
+        <v>8.215642482556708</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>8.233471211243319</v>
+        <v>8.234901432720093</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>6</v>
       </c>
       <c r="K129" t="n">
-        <v>8.33695754632191</v>
+        <v>8.338770570052079</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>6</v>
       </c>
       <c r="K130" t="n">
-        <v>8.659828082032606</v>
+        <v>8.661114516403142</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>6</v>
       </c>
       <c r="K131" t="n">
-        <v>8.955520418282028</v>
+        <v>8.957982002673143</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>9.117370986390577</v>
+        <v>9.118840462178738</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>9.182150333628899</v>
+        <v>9.184142659321292</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>6</v>
       </c>
       <c r="K134" t="n">
-        <v>9.502707810945383</v>
+        <v>9.503947719470569</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>6</v>
       </c>
       <c r="K135" t="n">
-        <v>9.58700817278682</v>
+        <v>9.601021663415642</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>9.600055061876473</v>
+        <v>9.601021663415642</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>9.666185798546529</v>
+        <v>9.667080517255647</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>9.747179920199084</v>
+        <v>9.748095555311115</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>9.919536055839442</v>
+        <v>9.920481651612979</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>6</v>
       </c>
       <c r="K140" t="n">
-        <v>10.03982707763049</v>
+        <v>10.03384085376461</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>6</v>
       </c>
       <c r="K141" t="n">
-        <v>10.10075936227274</v>
+        <v>10.04873175068141</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>6</v>
       </c>
       <c r="K142" t="n">
-        <v>10.18523871563691</v>
+        <v>10.1703113821572</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>6</v>
       </c>
       <c r="K143" t="n">
-        <v>10.18523871563691</v>
+        <v>10.1703113821572</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>10.3241301980949</v>
+        <v>10.32652469704417</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>6</v>
       </c>
       <c r="K145" t="n">
-        <v>10.3241301980949</v>
+        <v>10.32652469704417</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>10.72804752206529</v>
+        <v>10.73329757505697</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>10.82821853712411</v>
+        <v>10.83205391069262</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="K148" t="n">
-        <v>11.31153344108232</v>
+        <v>11.34493953621662</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>6</v>
       </c>
       <c r="K149" t="n">
-        <v>11.3428515747395</v>
+        <v>11.34493953621662</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>6</v>
       </c>
       <c r="K150" t="n">
-        <v>11.56598692004501</v>
+        <v>11.56684451772449</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>6</v>
       </c>
       <c r="K151" t="n">
-        <v>11.58221626307304</v>
+        <v>11.58198326305179</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>6</v>
       </c>
       <c r="K152" t="n">
-        <v>11.6068897425725</v>
+        <v>11.60728634568303</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>6</v>
       </c>
       <c r="K153" t="n">
-        <v>11.6490487157816</v>
+        <v>11.65030216584749</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>6</v>
       </c>
       <c r="K154" t="n">
-        <v>12.28759492419801</v>
+        <v>12.28927385385947</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>12.54621779554327</v>
+        <v>12.54816392343241</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>12.57078394962207</v>
+        <v>12.56367312450933</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>6</v>
       </c>
       <c r="K157" t="n">
-        <v>12.73187879407693</v>
+        <v>12.73286697894567</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>6</v>
       </c>
       <c r="K158" t="n">
-        <v>12.90081744954813</v>
+        <v>12.90108600673018</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>6</v>
       </c>
       <c r="K159" t="n">
-        <v>12.73729214372356</v>
+        <v>12.73686903582316</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>6</v>
       </c>
       <c r="K160" t="n">
-        <v>12.61379930677621</v>
+        <v>12.61285613536885</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>6</v>
       </c>
       <c r="K161" t="n">
-        <v>12.48481118538775</v>
+        <v>12.48423020315763</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>12.17667309377143</v>
+        <v>12.17615535638471</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>6</v>
       </c>
       <c r="K163" t="n">
-        <v>12.09432674237669</v>
+        <v>12.0939672988404</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="K164" t="n">
-        <v>12.31599521887282</v>
+        <v>12.30220165692974</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>6</v>
       </c>
       <c r="K165" t="n">
-        <v>12.5062115616939</v>
+        <v>12.50813670960662</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>6</v>
       </c>
       <c r="K166" t="n">
-        <v>13.12036788826173</v>
+        <v>13.12139488965561</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>6</v>
       </c>
       <c r="K167" t="n">
-        <v>13.1463425367316</v>
+        <v>13.1377199395177</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>13.18008131564125</v>
+        <v>13.18039755108718</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>13.40114512882637</v>
+        <v>13.40216427255851</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>6</v>
       </c>
       <c r="K170" t="n">
-        <v>13.51724608384559</v>
+        <v>13.51770449706086</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>6</v>
       </c>
       <c r="K171" t="n">
-        <v>13.51724608384559</v>
+        <v>13.51770449706086</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>6</v>
       </c>
       <c r="K172" t="n">
-        <v>13.45049177307704</v>
+        <v>13.42834726587935</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>6</v>
       </c>
       <c r="K173" t="n">
-        <v>13.41663382802796</v>
+        <v>13.42834726587935</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>6</v>
       </c>
       <c r="K174" t="n">
-        <v>13.1360587715864</v>
+        <v>13.13596054003147</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>6</v>
       </c>
       <c r="K175" t="n">
-        <v>12.383252203665</v>
+        <v>12.3818195935645</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>12.32503009871696</v>
+        <v>12.34488939642437</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>11.8644104980694</v>
+        <v>11.86363453966294</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>11.66991607980337</v>
+        <v>11.66917292052748</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>6</v>
       </c>
       <c r="K179" t="n">
-        <v>11.4397626168475</v>
+        <v>11.44003729032269</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>11.37121225770263</v>
+        <v>11.37095695966775</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>6</v>
       </c>
       <c r="K181" t="n">
-        <v>11.08346970895239</v>
+        <v>11.0824964530113</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>11.09012132545501</v>
+        <v>11.09009195586846</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>11.1133397312677</v>
+        <v>11.11346172376633</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>11.38285727695747</v>
+        <v>11.38295853545234</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>6</v>
       </c>
       <c r="K185" t="n">
-        <v>11.40930901230741</v>
+        <v>11.40906398075885</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="K186" t="n">
-        <v>11.63847912745985</v>
+        <v>11.63801176927609</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>7</v>
       </c>
       <c r="K187" t="n">
-        <v>12.23669714585852</v>
+        <v>12.23561229550869</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>7</v>
       </c>
       <c r="K188" t="n">
-        <v>12.32498885385217</v>
+        <v>12.32493800141896</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>7</v>
       </c>
       <c r="K189" t="n">
-        <v>12.6846002976039</v>
+        <v>12.68439321587084</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>7</v>
       </c>
       <c r="K190" t="n">
-        <v>13.02992558520946</v>
+        <v>13.02958147828541</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>7</v>
       </c>
       <c r="K191" t="n">
-        <v>13.11080079318839</v>
+        <v>13.10942074896131</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>7</v>
       </c>
       <c r="K192" t="n">
-        <v>13.23499422520247</v>
+        <v>13.21905420441579</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>7</v>
       </c>
       <c r="K193" t="n">
-        <v>13.38869754162123</v>
+        <v>13.41609389853743</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>7</v>
       </c>
       <c r="K194" t="n">
-        <v>13.84081620532295</v>
+        <v>13.85685042720981</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>7</v>
       </c>
       <c r="K195" t="n">
-        <v>13.85513475154574</v>
+        <v>13.85685042720981</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>7</v>
       </c>
       <c r="K196" t="n">
-        <v>13.85513475154574</v>
+        <v>13.85685042720981</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>7</v>
       </c>
       <c r="K197" t="n">
-        <v>13.89603621482746</v>
+        <v>13.90173162460115</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>7</v>
       </c>
       <c r="K198" t="n">
-        <v>13.08301745600236</v>
+        <v>13.08958004473499</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>7</v>
       </c>
       <c r="K199" t="n">
-        <v>13.08301745600236</v>
+        <v>13.08958004473499</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>7</v>
       </c>
       <c r="K200" t="n">
-        <v>12.79344106631639</v>
+        <v>12.78976864218879</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>7</v>
       </c>
       <c r="K201" t="n">
-        <v>12.79344106631639</v>
+        <v>12.78976864218879</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>12.00715379503883</v>
+        <v>12.02344956757194</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>7</v>
       </c>
       <c r="K203" t="n">
-        <v>11.12071911562041</v>
+        <v>11.35486375876084</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>7</v>
       </c>
       <c r="K204" t="n">
-        <v>10.85358927129134</v>
+        <v>10.84914955146178</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>7</v>
       </c>
       <c r="K205" t="n">
-        <v>9.459045729439039</v>
+        <v>9.465079945180731</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>7</v>
       </c>
       <c r="K206" t="n">
-        <v>9.437147962636711</v>
+        <v>9.429051361664438</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>7</v>
       </c>
       <c r="K207" t="n">
-        <v>9.54143291222257</v>
+        <v>9.541355830426482</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>7</v>
       </c>
       <c r="K208" t="n">
-        <v>9.625850753583549</v>
+        <v>9.630205530409832</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>7</v>
       </c>
       <c r="K209" t="n">
-        <v>9.625850753583549</v>
+        <v>9.630205530409832</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>7</v>
       </c>
       <c r="K210" t="n">
-        <v>12.38066397757235</v>
+        <v>12.33771936542497</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>7</v>
       </c>
       <c r="K211" t="n">
-        <v>12.71821880589731</v>
+        <v>12.68143979333274</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>7</v>
       </c>
       <c r="K212" t="n">
-        <v>13.44948705679101</v>
+        <v>13.44446385614669</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>7</v>
       </c>
       <c r="K213" t="n">
-        <v>14.21732025284459</v>
+        <v>14.02459428668939</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>7</v>
       </c>
       <c r="K214" t="n">
-        <v>14.21745677623078</v>
+        <v>14.21336218412485</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>7</v>
       </c>
       <c r="K215" t="n">
-        <v>14.21745677623078</v>
+        <v>14.21336218412485</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>7</v>
       </c>
       <c r="K216" t="n">
-        <v>14.25510820694356</v>
+        <v>14.23760632627079</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>7</v>
       </c>
       <c r="K217" t="n">
-        <v>14.48563426810835</v>
+        <v>14.48428152654683</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>7</v>
       </c>
       <c r="K218" t="n">
-        <v>14.41465342011496</v>
+        <v>14.41676964340713</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>7</v>
       </c>
       <c r="K219" t="n">
-        <v>14.41465342011496</v>
+        <v>14.41676964340713</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>7</v>
       </c>
       <c r="K220" t="n">
-        <v>14.39499340107542</v>
+        <v>14.4039811208747</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>7</v>
       </c>
       <c r="K221" t="n">
-        <v>14.408006382966</v>
+        <v>14.39115198493066</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>7</v>
       </c>
       <c r="K222" t="n">
-        <v>14.54077189549916</v>
+        <v>15.68537209978566</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>7</v>
       </c>
       <c r="K223" t="n">
-        <v>14.56706940849767</v>
+        <v>14.55141868468563</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>7</v>
       </c>
       <c r="K224" t="n">
-        <v>14.41123879058222</v>
+        <v>14.63775965186692</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>7</v>
       </c>
       <c r="K225" t="n">
-        <v>9.734247449587954</v>
+        <v>9.742891111081873</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>7</v>
       </c>
       <c r="K226" t="n">
-        <v>9.734247449587954</v>
+        <v>9.742891111081873</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>7</v>
       </c>
       <c r="K227" t="n">
-        <v>9.593812835277401</v>
+        <v>9.598140150086556</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>7</v>
       </c>
       <c r="K228" t="n">
-        <v>9.563180560247915</v>
+        <v>9.577943442830595</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>7</v>
       </c>
       <c r="K229" t="n">
-        <v>9.32658839506702</v>
+        <v>9.328574182929387</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>7</v>
       </c>
       <c r="K230" t="n">
-        <v>9.32658839506702</v>
+        <v>9.328574182929387</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>7</v>
       </c>
       <c r="K231" t="n">
-        <v>9.212777979173321</v>
+        <v>9.215841458343096</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>7</v>
       </c>
       <c r="K232" t="n">
-        <v>9.048349594171293</v>
+        <v>9.065450967498593</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>7</v>
       </c>
       <c r="K233" t="n">
-        <v>9.048349594171293</v>
+        <v>8.944815767177214</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>7</v>
       </c>
       <c r="K234" t="n">
-        <v>8.562581998394522</v>
+        <v>8.565077810158083</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>7</v>
       </c>
       <c r="K235" t="n">
-        <v>8.54224868104124</v>
+        <v>8.550860831439831</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>7</v>
       </c>
       <c r="K236" t="n">
-        <v>8.530053473915986</v>
+        <v>8.529971523309928</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>7</v>
       </c>
       <c r="K237" t="n">
-        <v>8.536025446984272</v>
+        <v>8.534832785725014</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>7</v>
       </c>
       <c r="K238" t="n">
-        <v>8.559446620806037</v>
+        <v>8.549542365725689</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>7</v>
       </c>
       <c r="K239" t="n">
-        <v>8.586175230134678</v>
+        <v>8.577751456745935</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>7</v>
       </c>
       <c r="K240" t="n">
-        <v>8.737150150974397</v>
+        <v>8.735219450043544</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>7</v>
       </c>
       <c r="K241" t="n">
-        <v>8.76378572010505</v>
+        <v>8.748361677410891</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>7</v>
       </c>
       <c r="K242" t="n">
-        <v>8.76378572010505</v>
+        <v>8.748361677410891</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>7</v>
       </c>
       <c r="K243" t="n">
-        <v>8.76378572010505</v>
+        <v>8.810267990394754</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>7</v>
       </c>
       <c r="K244" t="n">
-        <v>8.860497001708882</v>
+        <v>8.841626865901995</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>7</v>
       </c>
       <c r="K245" t="n">
-        <v>8.728049327441687</v>
+        <v>8.706355136818491</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>7</v>
       </c>
       <c r="K246" t="n">
-        <v>8.265998682229123</v>
+        <v>8.269488333551342</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>7</v>
       </c>
       <c r="K247" t="n">
-        <v>8.023206549470904</v>
+        <v>8.045862914088417</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>7</v>
       </c>
       <c r="K248" t="n">
-        <v>7.682841429451753</v>
+        <v>7.70126369523794</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>7</v>
       </c>
       <c r="K249" t="n">
-        <v>7.426705554602476</v>
+        <v>7.429158110036173</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>7</v>
       </c>
       <c r="K250" t="n">
-        <v>7.390699076518517</v>
+        <v>7.406152218319828</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>7</v>
       </c>
       <c r="K251" t="n">
-        <v>7.27884898883527</v>
+        <v>7.291847534290575</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>7</v>
       </c>
       <c r="K252" t="n">
-        <v>7.073104492826911</v>
+        <v>7.085970062187926</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>7</v>
       </c>
       <c r="K253" t="n">
-        <v>6.940037937728103</v>
+        <v>6.942005974260733</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>7</v>
       </c>
       <c r="K254" t="n">
-        <v>6.93016237048678</v>
+        <v>6.930549545885073</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>7</v>
       </c>
       <c r="K255" t="n">
-        <v>6.881720950445676</v>
+        <v>6.880799250615472</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>7</v>
       </c>
       <c r="K256" t="n">
-        <v>6.887369828723834</v>
+        <v>6.888694006086773</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>7</v>
       </c>
       <c r="K257" t="n">
-        <v>6.897370209718122</v>
+        <v>6.895701834256979</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>7</v>
       </c>
       <c r="K258" t="n">
-        <v>7.019634701549224</v>
+        <v>7.018718702796285</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>7</v>
       </c>
       <c r="K259" t="n">
-        <v>7.261734544884275</v>
+        <v>7.255915259470625</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>7</v>
       </c>
       <c r="K260" t="n">
-        <v>7.337199573793328</v>
+        <v>7.335757145170267</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>7</v>
       </c>
       <c r="K261" t="n">
-        <v>7.353648766155164</v>
+        <v>7.395306260371563</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
-        <v>7.697364158138308</v>
+        <v>7.684266951408063</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>7</v>
       </c>
       <c r="K263" t="n">
-        <v>7.813713083694449</v>
+        <v>7.812445957380925</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>7</v>
       </c>
       <c r="K264" t="n">
-        <v>7.852861725447755</v>
+        <v>7.852442855821411</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>7</v>
       </c>
       <c r="K265" t="n">
-        <v>7.809475589085111</v>
+        <v>7.804790645072968</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>7</v>
       </c>
       <c r="K266" t="n">
-        <v>7.801980325901026</v>
+        <v>7.804790645072968</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>7</v>
       </c>
       <c r="K267" t="n">
-        <v>7.754980503365975</v>
+        <v>7.757289974892627</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>7</v>
       </c>
       <c r="K268" t="n">
-        <v>7.754043892148252</v>
+        <v>7.753198775416064</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>7</v>
       </c>
       <c r="K269" t="n">
-        <v>7.766742730517447</v>
+        <v>7.811319883900175</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>7</v>
       </c>
       <c r="K270" t="n">
-        <v>7.905784414110376</v>
+        <v>7.896187374591876</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>7</v>
       </c>
       <c r="K271" t="n">
-        <v>7.905784414110376</v>
+        <v>7.947065880865615</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>7</v>
       </c>
       <c r="K272" t="n">
-        <v>8.091589868342119</v>
+        <v>8.091160802428435</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>7</v>
       </c>
       <c r="K273" t="n">
-        <v>8.091589868342119</v>
+        <v>8.091160802428435</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>7</v>
       </c>
       <c r="K274" t="n">
-        <v>8.094802967818806</v>
+        <v>8.094923772557038</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K275" t="n">
-        <v>7.88378320299368</v>
+        <v>7.887845131643867</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>7</v>
       </c>
       <c r="K276" t="n">
-        <v>7.88378320299368</v>
+        <v>7.887845131643867</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>7</v>
       </c>
       <c r="K277" t="n">
-        <v>7.750076640136291</v>
+        <v>7.754767982644371</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>7</v>
       </c>
       <c r="K278" t="n">
-        <v>7.615851548817426</v>
+        <v>7.620024938158743</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>7</v>
       </c>
       <c r="K279" t="n">
-        <v>7.4976540749409</v>
+        <v>7.501313960902893</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>7</v>
       </c>
       <c r="K280" t="n">
-        <v>7.399174672738896</v>
+        <v>7.385119377595603</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>7</v>
       </c>
       <c r="K281" t="n">
-        <v>7.172019078035414</v>
+        <v>7.157354591734371</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>7</v>
       </c>
       <c r="K282" t="n">
-        <v>7.022623340920935</v>
+        <v>7.024544672137996</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>7</v>
       </c>
       <c r="K283" t="n">
-        <v>7.022623340920935</v>
+        <v>7.024544672137996</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>7</v>
       </c>
       <c r="K284" t="n">
-        <v>6.949621456732038</v>
+        <v>6.958098631593606</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>7</v>
       </c>
       <c r="K285" t="n">
-        <v>6.744780477562138</v>
+        <v>6.745824529699249</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>7</v>
       </c>
       <c r="K286" t="n">
-        <v>6.716721062381463</v>
+        <v>6.711301953933487</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>7</v>
       </c>
       <c r="K287" t="n">
-        <v>6.662865397376675</v>
+        <v>6.664070680251434</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>7</v>
       </c>
       <c r="K288" t="n">
-        <v>6.633904050308234</v>
+        <v>6.628438016144022</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>7</v>
       </c>
       <c r="K289" t="n">
-        <v>6.636489709097011</v>
+        <v>6.653153305337002</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>7</v>
       </c>
       <c r="K290" t="n">
-        <v>6.811267640851021</v>
+        <v>6.806096181531817</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>7</v>
       </c>
       <c r="K291" t="n">
-        <v>6.811267640851021</v>
+        <v>6.806096181531817</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>7</v>
       </c>
       <c r="K292" t="n">
-        <v>6.811267640851021</v>
+        <v>6.806096181531817</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>7</v>
       </c>
       <c r="K293" t="n">
-        <v>7.237652280391756</v>
+        <v>7.234413896642751</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>7</v>
       </c>
       <c r="K294" t="n">
-        <v>7.370496241404817</v>
+        <v>7.436464405797164</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>7</v>
       </c>
       <c r="K295" t="n">
-        <v>7.439838427456145</v>
+        <v>7.436464405797164</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>7</v>
       </c>
       <c r="K296" t="n">
-        <v>7.476240368690293</v>
+        <v>7.459374670481116</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>7</v>
       </c>
       <c r="K297" t="n">
-        <v>7.678188940940187</v>
+        <v>7.663399082393298</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>7</v>
       </c>
       <c r="K298" t="n">
-        <v>7.733481435354341</v>
+        <v>7.730767181066641</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>7</v>
       </c>
       <c r="K299" t="n">
-        <v>7.759006721757935</v>
+        <v>7.747134464325244</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>7</v>
       </c>
       <c r="K300" t="n">
-        <v>7.804956245711396</v>
+        <v>7.802628451831043</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>7</v>
       </c>
       <c r="K301" t="n">
-        <v>7.804956245711396</v>
+        <v>7.802628451831043</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>7</v>
       </c>
       <c r="K302" t="n">
-        <v>7.848477482105796</v>
+        <v>7.851323757950896</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>7</v>
       </c>
       <c r="K303" t="n">
-        <v>7.821414167292595</v>
+        <v>7.79576681565711</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>7</v>
       </c>
       <c r="K304" t="n">
-        <v>7.821414167292595</v>
+        <v>7.79576681565711</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>7</v>
       </c>
       <c r="K305" t="n">
-        <v>7.676128669843547</v>
+        <v>7.678471005022509</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>7</v>
       </c>
       <c r="K306" t="n">
-        <v>7.607003620597352</v>
+        <v>7.609931305978408</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>7</v>
       </c>
       <c r="K307" t="n">
-        <v>7.582199511561298</v>
+        <v>7.594227882409046</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>7</v>
       </c>
       <c r="K308" t="n">
-        <v>7.513040273045318</v>
+        <v>7.522836802289743</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>7</v>
       </c>
       <c r="K309" t="n">
-        <v>7.465403287105601</v>
+        <v>7.465481402965496</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>7</v>
       </c>
       <c r="K310" t="n">
-        <v>7.381873541546802</v>
+        <v>7.384943791489403</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>7</v>
       </c>
       <c r="K311" t="n">
-        <v>7.381873541546802</v>
+        <v>7.384943791489403</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>7</v>
       </c>
       <c r="K312" t="n">
-        <v>7.34819049436848</v>
+        <v>7.36447856822238</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>7</v>
       </c>
       <c r="K313" t="n">
-        <v>7.34819049436848</v>
+        <v>7.36447856822238</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>7</v>
       </c>
       <c r="K314" t="n">
-        <v>7.153524269182269</v>
+        <v>7.156615059956872</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>7</v>
       </c>
       <c r="K315" t="n">
-        <v>7.108084786034201</v>
+        <v>7.029810944938665</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>7</v>
       </c>
       <c r="K316" t="n">
-        <v>7.026264001038359</v>
+        <v>7.029810944938665</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>7</v>
       </c>
       <c r="K317" t="n">
-        <v>6.830589873021131</v>
+        <v>6.839844961015226</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>7</v>
       </c>
       <c r="K318" t="n">
-        <v>6.830589873021131</v>
+        <v>6.839844961015226</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>7</v>
       </c>
       <c r="K319" t="n">
-        <v>6.677771599728734</v>
+        <v>6.660299542150244</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>7</v>
       </c>
       <c r="K320" t="n">
-        <v>6.618872689533801</v>
+        <v>6.594303538675203</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>7</v>
       </c>
       <c r="K321" t="n">
-        <v>6.576829319118065</v>
+        <v>6.58434003546021</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>7</v>
       </c>
       <c r="K322" t="n">
-        <v>6.548009539852067</v>
+        <v>6.549592541836081</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>7</v>
       </c>
       <c r="K323" t="n">
-        <v>6.497439067214024</v>
+        <v>6.469510150933785</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>7</v>
       </c>
       <c r="K324" t="n">
-        <v>6.453909886628229</v>
+        <v>6.460414444690698</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>7</v>
       </c>
       <c r="K325" t="n">
-        <v>6.412272716443038</v>
+        <v>6.419938671774504</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>7</v>
       </c>
       <c r="K326" t="n">
-        <v>6.26656824033005</v>
+        <v>6.268922249781057</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>7</v>
       </c>
       <c r="K327" t="n">
-        <v>6.26656824033005</v>
+        <v>6.268922249781057</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>7</v>
       </c>
       <c r="K328" t="n">
-        <v>6.179887083221361</v>
+        <v>6.190925879339379</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>7</v>
       </c>
       <c r="K329" t="n">
-        <v>6.066013995221533</v>
+        <v>6.068611681953345</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>7</v>
       </c>
       <c r="K330" t="n">
-        <v>6.041663888962099</v>
+        <v>6.053122122734557</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>7</v>
       </c>
       <c r="K331" t="n">
-        <v>5.999590089565928</v>
+        <v>6.00209000715434</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>7</v>
       </c>
       <c r="K332" t="n">
-        <v>5.937678631716218</v>
+        <v>5.926461158265312</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>7</v>
       </c>
       <c r="K333" t="n">
-        <v>5.831710507891906</v>
+        <v>5.822374149868225</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>7</v>
       </c>
       <c r="K334" t="n">
-        <v>5.789907504334945</v>
+        <v>5.791157578200315</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>7</v>
       </c>
       <c r="K335" t="n">
-        <v>5.76138303069191</v>
+        <v>5.762324100490123</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>7</v>
       </c>
       <c r="K336" t="n">
-        <v>5.739746166575894</v>
+        <v>5.743382176924778</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>7</v>
       </c>
       <c r="K337" t="n">
-        <v>5.711796318421265</v>
+        <v>5.712773000595837</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>7</v>
       </c>
       <c r="K338" t="n">
-        <v>5.681233299173138</v>
+        <v>5.682736709411799</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>7</v>
       </c>
       <c r="K339" t="n">
-        <v>5.603248403126044</v>
+        <v>5.614247369059662</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>7</v>
       </c>
       <c r="K340" t="n">
-        <v>5.603248403126044</v>
+        <v>5.614247369059662</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>7</v>
       </c>
       <c r="K341" t="n">
-        <v>5.450425930637783</v>
+        <v>5.466218631771539</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>7</v>
       </c>
       <c r="K342" t="n">
-        <v>5.295686149951442</v>
+        <v>5.305409229519007</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>7</v>
       </c>
       <c r="K343" t="n">
-        <v>5.33125954182276</v>
+        <v>5.33604241965882</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>7</v>
       </c>
       <c r="K344" t="n">
-        <v>5.366807301755229</v>
+        <v>5.35960892797343</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>7</v>
       </c>
       <c r="K345" t="n">
-        <v>5.377034269525428</v>
+        <v>5.387142983451969</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>7</v>
       </c>
       <c r="K346" t="n">
-        <v>5.377034269525428</v>
+        <v>5.40774612996696</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>8</v>
       </c>
       <c r="K347" t="n">
-        <v>5.493321358906104</v>
+        <v>5.495254424889437</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>8</v>
       </c>
       <c r="K348" t="n">
-        <v>5.739213655571318</v>
+        <v>5.719426062454195</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>8</v>
       </c>
       <c r="K349" t="n">
-        <v>5.718485801995851</v>
+        <v>5.71477537667693</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>8</v>
       </c>
       <c r="K350" t="n">
-        <v>6.034682340706093</v>
+        <v>6.025982933699755</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>8</v>
       </c>
       <c r="K351" t="n">
-        <v>6.034682340706093</v>
+        <v>6.025982933699755</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>8</v>
       </c>
       <c r="K352" t="n">
-        <v>6.245914570268079</v>
+        <v>6.234619078969213</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>8</v>
       </c>
       <c r="K353" t="n">
-        <v>6.502694223379855</v>
+        <v>6.485736775517078</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>8</v>
       </c>
       <c r="K354" t="n">
-        <v>7.256613841239154</v>
+        <v>7.234770962076014</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>8</v>
       </c>
       <c r="K355" t="n">
-        <v>7.695025695766322</v>
+        <v>7.672976275891726</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>8</v>
       </c>
       <c r="K356" t="n">
-        <v>7.695025695766322</v>
+        <v>8.119729253152988</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>8</v>
       </c>
       <c r="K357" t="n">
-        <v>8.664252001705387</v>
+        <v>8.633550049229511</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>8</v>
       </c>
       <c r="K358" t="n">
-        <v>10.31761787795666</v>
+        <v>10.28176259327004</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>8</v>
       </c>
       <c r="K359" t="n">
-        <v>11.98752028384219</v>
+        <v>11.96922890910575</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>8</v>
       </c>
       <c r="K360" t="n">
-        <v>11.98752028384219</v>
+        <v>11.96922890910575</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>8</v>
       </c>
       <c r="K361" t="n">
-        <v>12.36142561437111</v>
+        <v>12.34163120238057</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>8</v>
       </c>
       <c r="K362" t="n">
-        <v>13.08285414266947</v>
+        <v>13.0776580985654</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>8</v>
       </c>
       <c r="K363" t="n">
-        <v>13.14525042021814</v>
+        <v>13.14115246713863</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>8</v>
       </c>
       <c r="K364" t="n">
-        <v>5.743707107682947</v>
+        <v>5.753110350645893</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>8</v>
       </c>
       <c r="K365" t="n">
-        <v>5.743707107682947</v>
+        <v>5.753110350645893</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>8</v>
       </c>
       <c r="K366" t="n">
-        <v>5.472423596824576</v>
+        <v>5.474035536245027</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>8</v>
       </c>
       <c r="K367" t="n">
-        <v>5.44759759738344</v>
+        <v>5.448799733400486</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>8</v>
       </c>
       <c r="K368" t="n">
-        <v>5.638096099423151</v>
+        <v>5.63237288606325</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>8</v>
       </c>
       <c r="K369" t="n">
-        <v>5.638096099423151</v>
+        <v>5.63237288606325</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>8</v>
       </c>
       <c r="K370" t="n">
-        <v>6.13111520268537</v>
+        <v>6.125556866389611</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>8</v>
       </c>
       <c r="K371" t="n">
-        <v>6.3448781535809</v>
+        <v>6.344098001927277</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>8</v>
       </c>
       <c r="K372" t="n">
-        <v>6.328314175409814</v>
+        <v>6.329905079064085</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>8</v>
       </c>
       <c r="K373" t="n">
-        <v>6.328314175409814</v>
+        <v>6.329905079064085</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>8</v>
       </c>
       <c r="K374" t="n">
-        <v>6.28695157496068</v>
+        <v>6.290064121017294</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>8</v>
       </c>
       <c r="K375" t="n">
-        <v>5.988216228835467</v>
+        <v>5.996778997826052</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>8</v>
       </c>
       <c r="K376" t="n">
-        <v>5.834892129221482</v>
+        <v>5.843670125452085</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>8</v>
       </c>
       <c r="K377" t="n">
-        <v>5.684259059242199</v>
+        <v>5.692795068263097</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>8</v>
       </c>
       <c r="K378" t="n">
-        <v>5.422062151665051</v>
+        <v>5.427674035693217</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>8</v>
       </c>
       <c r="K379" t="n">
-        <v>5.422062151665051</v>
+        <v>5.427674035693217</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>8</v>
       </c>
       <c r="K380" t="n">
-        <v>5.344683487756081</v>
+        <v>5.348666451675093</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>8</v>
       </c>
       <c r="K381" t="n">
-        <v>5.074943128878695</v>
+        <v>5.077030209508068</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>8</v>
       </c>
       <c r="K382" t="n">
-        <v>5.074943128878695</v>
+        <v>5.077030209508068</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>8</v>
       </c>
       <c r="K383" t="n">
-        <v>5.037899914450541</v>
+        <v>5.036336852181534</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>8</v>
       </c>
       <c r="K384" t="n">
-        <v>5.059895125495137</v>
+        <v>5.058706344227933</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>8</v>
       </c>
       <c r="K385" t="n">
-        <v>5.082790975570815</v>
+        <v>5.081392526125048</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>8</v>
       </c>
       <c r="K386" t="n">
-        <v>5.086811338186689</v>
+        <v>5.08795564673822</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>8</v>
       </c>
       <c r="K387" t="n">
-        <v>5.063189107111755</v>
+        <v>5.063854722044542</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>8</v>
       </c>
       <c r="K388" t="n">
-        <v>5.056011752234394</v>
+        <v>5.055181791082892</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>8</v>
       </c>
       <c r="K389" t="n">
-        <v>5.062778848704109</v>
+        <v>5.062396491905896</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>8</v>
       </c>
       <c r="K390" t="n">
-        <v>5.090683402143662</v>
+        <v>5.089392770036743</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>8</v>
       </c>
       <c r="K391" t="n">
-        <v>5.090683402143662</v>
+        <v>5.089392770036743</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>8</v>
       </c>
       <c r="K392" t="n">
-        <v>5.202326026581845</v>
+        <v>5.200333848839695</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>8</v>
       </c>
       <c r="K393" t="n">
-        <v>5.290336999426789</v>
+        <v>5.287571719187256</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>8</v>
       </c>
       <c r="K394" t="n">
-        <v>5.330232900274008</v>
+        <v>5.327812711011015</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>8</v>
       </c>
       <c r="K395" t="n">
-        <v>5.453334636126282</v>
+        <v>5.45077685700736</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>8</v>
       </c>
       <c r="K396" t="n">
-        <v>5.486481245434981</v>
+        <v>5.484546853066156</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>8</v>
       </c>
       <c r="K397" t="n">
-        <v>5.63865396421261</v>
+        <v>5.63426561192883</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>8</v>
       </c>
       <c r="K398" t="n">
-        <v>5.63865396421261</v>
+        <v>5.63426561192883</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>8</v>
       </c>
       <c r="K399" t="n">
-        <v>5.77621278739655</v>
+        <v>5.775424839693248</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>8</v>
       </c>
       <c r="K400" t="n">
-        <v>5.752968380443138</v>
+        <v>5.689932621896061</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>8</v>
       </c>
       <c r="K401" t="n">
-        <v>5.684019831668254</v>
+        <v>5.689932621896061</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>8</v>
       </c>
       <c r="K402" t="n">
-        <v>5.583492488494437</v>
+        <v>5.590884409788842</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>8</v>
       </c>
       <c r="K403" t="n">
-        <v>5.166917734529678</v>
+        <v>5.173997526693493</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>8</v>
       </c>
       <c r="K404" t="n">
-        <v>5.068552258259398</v>
+        <v>5.075665259238299</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>8</v>
       </c>
       <c r="K405" t="n">
-        <v>4.972447535733636</v>
+        <v>4.979603155641992</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>8</v>
       </c>
       <c r="K406" t="n">
-        <v>4.793131892164692</v>
+        <v>4.802023799932601</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>8</v>
       </c>
       <c r="K407" t="n">
-        <v>4.630084444582541</v>
+        <v>4.634982634401516</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>8</v>
       </c>
       <c r="K408" t="n">
-        <v>4.630084444582541</v>
+        <v>4.634982634401516</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>8</v>
       </c>
       <c r="K409" t="n">
-        <v>4.630084444582541</v>
+        <v>4.634982634401516</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>8</v>
       </c>
       <c r="K410" t="n">
-        <v>4.630084444582541</v>
+        <v>4.634982634401516</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>8</v>
       </c>
       <c r="K411" t="n">
-        <v>4.551289136132044</v>
+        <v>4.552415445694953</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>8</v>
       </c>
       <c r="K412" t="n">
-        <v>4.317192505241925</v>
+        <v>4.286131849231502</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>8</v>
       </c>
       <c r="K413" t="n">
-        <v>4.283860074177524</v>
+        <v>4.286131849231502</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>8</v>
       </c>
       <c r="K414" t="n">
-        <v>4.248525872342472</v>
+        <v>4.248888736848033</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>8</v>
       </c>
       <c r="K415" t="n">
-        <v>4.248122682432491</v>
+        <v>4.247368540041877</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>8</v>
       </c>
       <c r="K416" t="n">
-        <v>4.248122682432491</v>
+        <v>4.260807841753912</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>8</v>
       </c>
       <c r="K417" t="n">
-        <v>4.381684588450497</v>
+        <v>4.441656920677191</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>8</v>
       </c>
       <c r="K418" t="n">
-        <v>4.446305116881335</v>
+        <v>4.441656920677191</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>8</v>
       </c>
       <c r="K419" t="n">
-        <v>4.508404138533302</v>
+        <v>4.503973247815932</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>8</v>
       </c>
       <c r="K420" t="n">
-        <v>4.644104378854511</v>
+        <v>4.640433584475184</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>8</v>
       </c>
       <c r="K421" t="n">
-        <v>4.644104378854511</v>
+        <v>4.640433584475184</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>8</v>
       </c>
       <c r="K422" t="n">
-        <v>4.730817518354133</v>
+        <v>4.721598741308307</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>8</v>
       </c>
       <c r="K423" t="n">
-        <v>4.720635905636274</v>
+        <v>4.721598741308307</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>8</v>
       </c>
       <c r="K424" t="n">
-        <v>4.720635905636274</v>
+        <v>4.721598741308307</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>8</v>
       </c>
       <c r="K425" t="n">
-        <v>4.696478134758685</v>
+        <v>4.699461833947534</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>8</v>
       </c>
       <c r="K426" t="n">
-        <v>4.660851789883031</v>
+        <v>4.663519002677985</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>8</v>
       </c>
       <c r="K427" t="n">
-        <v>4.63275856616254</v>
+        <v>4.634317651026816</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>8</v>
       </c>
       <c r="K428" t="n">
-        <v>4.568872581714889</v>
+        <v>4.573162546906508</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>8</v>
       </c>
       <c r="K429" t="n">
-        <v>4.568872581714889</v>
+        <v>4.573162546906508</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>8</v>
       </c>
       <c r="K430" t="n">
-        <v>4.348694094609902</v>
+        <v>4.359638275576192</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>8</v>
       </c>
       <c r="K431" t="n">
-        <v>4.000775197122946</v>
+        <v>4.004936795835266</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>8</v>
       </c>
       <c r="K432" t="n">
-        <v>4.000775197122946</v>
+        <v>4.004936795835266</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>8</v>
       </c>
       <c r="K433" t="n">
-        <v>4.000775197122946</v>
+        <v>4.004936795835266</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>8</v>
       </c>
       <c r="K434" t="n">
-        <v>4.000775197122946</v>
+        <v>4.004936795835266</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>8</v>
       </c>
       <c r="K435" t="n">
-        <v>3.963685742991612</v>
+        <v>3.954711182852985</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>8</v>
       </c>
       <c r="K436" t="n">
-        <v>4.076573269146983</v>
+        <v>4.071721943889777</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>8</v>
       </c>
       <c r="K437" t="n">
-        <v>4.114773050740846</v>
+        <v>4.112563387934604</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>8</v>
       </c>
       <c r="K438" t="n">
-        <v>4.169595700636805</v>
+        <v>4.167984366394091</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>8</v>
       </c>
       <c r="K439" t="n">
-        <v>4.195283773379092</v>
+        <v>4.193374833234868</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>8</v>
       </c>
       <c r="K440" t="n">
-        <v>4.230768243059676</v>
+        <v>4.230649096407671</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>8</v>
       </c>
       <c r="K441" t="n">
-        <v>4.21839977109265</v>
+        <v>4.220181140182767</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>8</v>
       </c>
       <c r="K442" t="n">
-        <v>4.119743195256251</v>
+        <v>4.124084794079952</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>8</v>
       </c>
       <c r="K443" t="n">
-        <v>4.049129284306339</v>
+        <v>4.054270027511654</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>8</v>
       </c>
       <c r="K444" t="n">
-        <v>4.049129284306339</v>
+        <v>4.054270027511654</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>8</v>
       </c>
       <c r="K445" t="n">
-        <v>4.049129284306339</v>
+        <v>3.973458984024082</v>
       </c>
     </row>
     <row r="446">
@@ -18727,7 +18727,7 @@
         <v>8</v>
       </c>
       <c r="K446" t="n">
-        <v>3.878580089175507</v>
+        <v>3.88528173717376</v>
       </c>
     </row>
     <row r="447">
@@ -18768,7 +18768,7 @@
         <v>8</v>
       </c>
       <c r="K447" t="n">
-        <v>3.77365944628656</v>
+        <v>3.780763688913944</v>
       </c>
     </row>
     <row r="448">
@@ -18809,7 +18809,7 @@
         <v>8</v>
       </c>
       <c r="K448" t="n">
-        <v>3.673582229944924</v>
+        <v>3.680240964029584</v>
       </c>
     </row>
     <row r="449">
@@ -18850,7 +18850,7 @@
         <v>8</v>
       </c>
       <c r="K449" t="n">
-        <v>3.673582229944924</v>
+        <v>3.680240964029584</v>
       </c>
     </row>
     <row r="450">
@@ -18891,7 +18891,7 @@
         <v>8</v>
       </c>
       <c r="K450" t="n">
-        <v>3.458812267481967</v>
+        <v>3.460572678971413</v>
       </c>
     </row>
     <row r="451">
@@ -18932,7 +18932,7 @@
         <v>8</v>
       </c>
       <c r="K451" t="n">
-        <v>3.411417218067499</v>
+        <v>3.413030947426391</v>
       </c>
     </row>
     <row r="452">
@@ -18973,7 +18973,7 @@
         <v>8</v>
       </c>
       <c r="K452" t="n">
-        <v>3.360305224853007</v>
+        <v>3.362603159324031</v>
       </c>
     </row>
     <row r="453">
@@ -19014,7 +19014,7 @@
         <v>8</v>
       </c>
       <c r="K453" t="n">
-        <v>3.360305224853007</v>
+        <v>3.362603159324031</v>
       </c>
     </row>
     <row r="454">
@@ -19055,7 +19055,7 @@
         <v>8</v>
       </c>
       <c r="K454" t="n">
-        <v>3.362139932279085</v>
+        <v>3.360001613419306</v>
       </c>
     </row>
     <row r="455">
@@ -19096,7 +19096,7 @@
         <v>8</v>
       </c>
       <c r="K455" t="n">
-        <v>3.362139932279085</v>
+        <v>3.360001613419306</v>
       </c>
     </row>
     <row r="456">
@@ -19137,7 +19137,7 @@
         <v>8</v>
       </c>
       <c r="K456" t="n">
-        <v>3.390941120633167</v>
+        <v>3.388997846814831</v>
       </c>
     </row>
     <row r="457">
@@ -19178,7 +19178,7 @@
         <v>8</v>
       </c>
       <c r="K457" t="n">
-        <v>3.44677272873193</v>
+        <v>3.444712817103581</v>
       </c>
     </row>
     <row r="458">
@@ -19219,7 +19219,7 @@
         <v>8</v>
       </c>
       <c r="K458" t="n">
-        <v>3.505285510518358</v>
+        <v>3.50322764095065</v>
       </c>
     </row>
     <row r="459">
@@ -19260,7 +19260,7 @@
         <v>8</v>
       </c>
       <c r="K459" t="n">
-        <v>3.531638048210043</v>
+        <v>3.561862329035114</v>
       </c>
     </row>
     <row r="460">
@@ -19301,7 +19301,7 @@
         <v>8</v>
       </c>
       <c r="K460" t="n">
-        <v>3.531638048210043</v>
+        <v>3.561862329035114</v>
       </c>
     </row>
     <row r="461">
@@ -19342,7 +19342,7 @@
         <v>8</v>
       </c>
       <c r="K461" t="n">
-        <v>3.84671606152053</v>
+        <v>3.842283267744739</v>
       </c>
     </row>
     <row r="462">
@@ -19383,7 +19383,7 @@
         <v>8</v>
       </c>
       <c r="K462" t="n">
-        <v>3.84671606152053</v>
+        <v>3.842283267744739</v>
       </c>
     </row>
     <row r="463">
@@ -19424,7 +19424,7 @@
         <v>8</v>
       </c>
       <c r="K463" t="n">
-        <v>3.901632372827883</v>
+        <v>3.898121634011583</v>
       </c>
     </row>
     <row r="464">
@@ -19465,7 +19465,7 @@
         <v>8</v>
       </c>
       <c r="K464" t="n">
-        <v>4.006885621268348</v>
+        <v>4.00498668634224</v>
       </c>
     </row>
     <row r="465">
@@ -19506,7 +19506,7 @@
         <v>8</v>
       </c>
       <c r="K465" t="n">
-        <v>4.02457142298111</v>
+        <v>4.024027989218543</v>
       </c>
     </row>
     <row r="466">
@@ -19547,7 +19547,7 @@
         <v>8</v>
       </c>
       <c r="K466" t="n">
-        <v>4.021808977162433</v>
+        <v>4.02245390773204</v>
       </c>
     </row>
     <row r="467">
@@ -19588,7 +19588,7 @@
         <v>8</v>
       </c>
       <c r="K467" t="n">
-        <v>4.016032277020198</v>
+        <v>4.015761826483935</v>
       </c>
     </row>
     <row r="468">
@@ -19629,7 +19629,7 @@
         <v>8</v>
       </c>
       <c r="K468" t="n">
-        <v>4.013815303742128</v>
+        <v>4.01486498034263</v>
       </c>
     </row>
     <row r="469">
@@ -19670,7 +19670,7 @@
         <v>8</v>
       </c>
       <c r="K469" t="n">
-        <v>3.98723716805063</v>
+        <v>3.990158871998295</v>
       </c>
     </row>
     <row r="470">
@@ -19711,7 +19711,7 @@
         <v>8</v>
       </c>
       <c r="K470" t="n">
-        <v>3.94306443314971</v>
+        <v>3.94651569540322</v>
       </c>
     </row>
     <row r="471">
@@ -19752,7 +19752,7 @@
         <v>8</v>
       </c>
       <c r="K471" t="n">
-        <v>3.897084353523008</v>
+        <v>3.900713429722123</v>
       </c>
     </row>
     <row r="472">
@@ -19793,7 +19793,7 @@
         <v>8</v>
       </c>
       <c r="K472" t="n">
-        <v>3.897084353523008</v>
+        <v>3.900713429722123</v>
       </c>
     </row>
     <row r="473">
@@ -19834,7 +19834,7 @@
         <v>8</v>
       </c>
       <c r="K473" t="n">
-        <v>3.785921917000738</v>
+        <v>3.790292271413379</v>
       </c>
     </row>
     <row r="474">
@@ -19875,7 +19875,7 @@
         <v>8</v>
       </c>
       <c r="K474" t="n">
-        <v>3.725385164059887</v>
+        <v>3.726227313066196</v>
       </c>
     </row>
     <row r="475">
@@ -19916,7 +19916,7 @@
         <v>8</v>
       </c>
       <c r="K475" t="n">
-        <v>3.708968087059856</v>
+        <v>3.710657079799133</v>
       </c>
     </row>
     <row r="476">
@@ -19957,7 +19957,7 @@
         <v>8</v>
       </c>
       <c r="K476" t="n">
-        <v>3.641933092297638</v>
+        <v>3.643721866801754</v>
       </c>
     </row>
     <row r="477">
@@ -19998,7 +19998,7 @@
         <v>8</v>
       </c>
       <c r="K477" t="n">
-        <v>3.641933092297638</v>
+        <v>3.643721866801754</v>
       </c>
     </row>
     <row r="478">
@@ -20039,7 +20039,7 @@
         <v>8</v>
       </c>
       <c r="K478" t="n">
-        <v>3.721090075727334</v>
+        <v>3.716455252740593</v>
       </c>
     </row>
     <row r="479">
@@ -20080,7 +20080,7 @@
         <v>8</v>
       </c>
       <c r="K479" t="n">
-        <v>3.784774783008613</v>
+        <v>3.780265446499381</v>
       </c>
     </row>
     <row r="480">
@@ -20121,7 +20121,7 @@
         <v>8</v>
       </c>
       <c r="K480" t="n">
-        <v>4.096633072741223</v>
+        <v>4.089401995982592</v>
       </c>
     </row>
     <row r="481">
@@ -20162,7 +20162,7 @@
         <v>8</v>
       </c>
       <c r="K481" t="n">
-        <v>4.202954389808656</v>
+        <v>4.195526394536419</v>
       </c>
     </row>
     <row r="482">
@@ -20203,7 +20203,7 @@
         <v>8</v>
       </c>
       <c r="K482" t="n">
-        <v>4.30660550275456</v>
+        <v>4.29904609509695</v>
       </c>
     </row>
     <row r="483">
@@ -20244,7 +20244,7 @@
         <v>8</v>
       </c>
       <c r="K483" t="n">
-        <v>4.30660550275456</v>
+        <v>4.29904609509695</v>
       </c>
     </row>
     <row r="484">
@@ -20285,7 +20285,7 @@
         <v>8</v>
       </c>
       <c r="K484" t="n">
-        <v>4.513375044525477</v>
+        <v>4.555720603538881</v>
       </c>
     </row>
     <row r="485">
@@ -20326,7 +20326,7 @@
         <v>8</v>
       </c>
       <c r="K485" t="n">
-        <v>4.557517060336521</v>
+        <v>4.555720603538881</v>
       </c>
     </row>
     <row r="486">
@@ -20367,7 +20367,7 @@
         <v>8</v>
       </c>
       <c r="K486" t="n">
-        <v>4.678820611758199</v>
+        <v>4.67615370469082</v>
       </c>
     </row>
     <row r="487">
@@ -20408,7 +20408,7 @@
         <v>8</v>
       </c>
       <c r="K487" t="n">
-        <v>4.708592220356953</v>
+        <v>4.706637081291499</v>
       </c>
     </row>
     <row r="488">
@@ -20449,7 +20449,7 @@
         <v>8</v>
       </c>
       <c r="K488" t="n">
-        <v>4.724426744361056</v>
+        <v>4.724307814878809</v>
       </c>
     </row>
     <row r="489">
@@ -20490,7 +20490,7 @@
         <v>8</v>
       </c>
       <c r="K489" t="n">
-        <v>4.724426744361056</v>
+        <v>4.724307814878809</v>
       </c>
     </row>
     <row r="490">
@@ -20531,7 +20531,7 @@
         <v>8</v>
       </c>
       <c r="K490" t="n">
-        <v>4.656125941029692</v>
+        <v>4.660628404081873</v>
       </c>
     </row>
     <row r="491">
@@ -20572,7 +20572,7 @@
         <v>8</v>
       </c>
       <c r="K491" t="n">
-        <v>4.411095779890414</v>
+        <v>4.419661949786981</v>
       </c>
     </row>
     <row r="492">
@@ -20613,7 +20613,7 @@
         <v>8</v>
       </c>
       <c r="K492" t="n">
-        <v>4.297641820216116</v>
+        <v>4.306373006485419</v>
       </c>
     </row>
     <row r="493">
@@ -20654,7 +20654,7 @@
         <v>8</v>
       </c>
       <c r="K493" t="n">
-        <v>4.099022145119758</v>
+        <v>4.105853278128054</v>
       </c>
     </row>
     <row r="494">
@@ -20695,7 +20695,7 @@
         <v>8</v>
       </c>
       <c r="K494" t="n">
-        <v>3.929321471476446</v>
+        <v>3.935028149594848</v>
       </c>
     </row>
     <row r="495">
@@ -20736,7 +20736,7 @@
         <v>8</v>
       </c>
       <c r="K495" t="n">
-        <v>3.929321471476446</v>
+        <v>3.935028149594848</v>
       </c>
     </row>
     <row r="496">
@@ -20777,7 +20777,7 @@
         <v>8</v>
       </c>
       <c r="K496" t="n">
-        <v>3.721302845300565</v>
+        <v>3.724946914200841</v>
       </c>
     </row>
     <row r="497">
@@ -20818,7 +20818,7 @@
         <v>8</v>
       </c>
       <c r="K497" t="n">
-        <v>3.679244037714437</v>
+        <v>3.682453318001541</v>
       </c>
     </row>
     <row r="498">
@@ -20859,7 +20859,7 @@
         <v>8</v>
       </c>
       <c r="K498" t="n">
-        <v>3.651415588779662</v>
+        <v>3.652906095687809</v>
       </c>
     </row>
     <row r="499">
@@ -20900,7 +20900,7 @@
         <v>8</v>
       </c>
       <c r="K499" t="n">
-        <v>3.633479341229477</v>
+        <v>3.635205281465438</v>
       </c>
     </row>
     <row r="500">
@@ -20941,7 +20941,7 @@
         <v>8</v>
       </c>
       <c r="K500" t="n">
-        <v>3.605550544155671</v>
+        <v>3.607930783145811</v>
       </c>
     </row>
     <row r="501">
@@ -20982,7 +20982,7 @@
         <v>8</v>
       </c>
       <c r="K501" t="n">
-        <v>3.570487396711592</v>
+        <v>3.573978759312188</v>
       </c>
     </row>
     <row r="502">
@@ -21023,7 +21023,7 @@
         <v>8</v>
       </c>
       <c r="K502" t="n">
-        <v>3.475247930948995</v>
+        <v>3.47866977571722</v>
       </c>
     </row>
     <row r="503">
@@ -21064,7 +21064,7 @@
         <v>8</v>
       </c>
       <c r="K503" t="n">
-        <v>3.432003283421213</v>
+        <v>3.432051183458465</v>
       </c>
     </row>
     <row r="504">
@@ -21105,7 +21105,7 @@
         <v>8</v>
       </c>
       <c r="K504" t="n">
-        <v>3.335979393489086</v>
+        <v>3.33453128577536</v>
       </c>
     </row>
     <row r="505">
@@ -21146,7 +21146,7 @@
         <v>8</v>
       </c>
       <c r="K505" t="n">
-        <v>3.335979393489086</v>
+        <v>3.33453128577536</v>
       </c>
     </row>
     <row r="506">
@@ -21187,7 +21187,7 @@
         <v>8</v>
       </c>
       <c r="K506" t="n">
-        <v>3.335979393489086</v>
+        <v>3.33453128577536</v>
       </c>
     </row>
     <row r="507">
@@ -21228,7 +21228,7 @@
         <v>8</v>
       </c>
       <c r="K507" t="n">
-        <v>3.202392468823748</v>
+        <v>3.205080866695542</v>
       </c>
     </row>
     <row r="508">
@@ -21269,7 +21269,7 @@
         <v>8</v>
       </c>
       <c r="K508" t="n">
-        <v>3.202392468823748</v>
+        <v>3.205080866695542</v>
       </c>
     </row>
     <row r="509">
@@ -21310,7 +21310,7 @@
         <v>8</v>
       </c>
       <c r="K509" t="n">
-        <v>3.131272868337079</v>
+        <v>3.13226713402056</v>
       </c>
     </row>
     <row r="510">
@@ -21351,7 +21351,7 @@
         <v>8</v>
       </c>
       <c r="K510" t="n">
-        <v>3.15928075987673</v>
+        <v>3.156673183750866</v>
       </c>
     </row>
     <row r="511">
@@ -21392,7 +21392,7 @@
         <v>8</v>
       </c>
       <c r="K511" t="n">
-        <v>3.15928075987673</v>
+        <v>3.156673183750866</v>
       </c>
     </row>
     <row r="512">
@@ -21433,7 +21433,7 @@
         <v>8</v>
       </c>
       <c r="K512" t="n">
-        <v>3.2380294991384</v>
+        <v>3.24208282446576</v>
       </c>
     </row>
     <row r="513">
@@ -21474,7 +21474,7 @@
         <v>8</v>
       </c>
       <c r="K513" t="n">
-        <v>3.2425052519939</v>
+        <v>3.24208282446576</v>
       </c>
     </row>
     <row r="514">
@@ -21515,7 +21515,7 @@
         <v>8</v>
       </c>
       <c r="K514" t="n">
-        <v>3.259705481976483</v>
+        <v>3.257211468439511</v>
       </c>
     </row>
     <row r="515">
@@ -21556,7 +21556,7 @@
         <v>8</v>
       </c>
       <c r="K515" t="n">
-        <v>3.396370479907137</v>
+        <v>3.39222295456804</v>
       </c>
     </row>
     <row r="516">
@@ -21597,7 +21597,7 @@
         <v>8</v>
       </c>
       <c r="K516" t="n">
-        <v>3.396370479907137</v>
+        <v>3.39222295456804</v>
       </c>
     </row>
     <row r="517">
@@ -21638,7 +21638,7 @@
         <v>8</v>
       </c>
       <c r="K517" t="n">
-        <v>3.396370479907137</v>
+        <v>3.44723748729929</v>
       </c>
     </row>
     <row r="518">
@@ -21679,7 +21679,7 @@
         <v>8</v>
       </c>
       <c r="K518" t="n">
-        <v>3.452424258023028</v>
+        <v>3.44723748729929</v>
       </c>
     </row>
     <row r="519">
@@ -21720,7 +21720,7 @@
         <v>8</v>
       </c>
       <c r="K519" t="n">
-        <v>3.571295521839088</v>
+        <v>3.567594561439599</v>
       </c>
     </row>
     <row r="520">
@@ -21761,7 +21761,7 @@
         <v>8</v>
       </c>
       <c r="K520" t="n">
-        <v>3.680623283211972</v>
+        <v>3.677204685537207</v>
       </c>
     </row>
     <row r="521">
@@ -21802,7 +21802,7 @@
         <v>8</v>
       </c>
       <c r="K521" t="n">
-        <v>3.795105184281383</v>
+        <v>3.794548191502888</v>
       </c>
     </row>
     <row r="522">
@@ -21843,7 +21843,7 @@
         <v>8</v>
       </c>
       <c r="K522" t="n">
-        <v>3.795105184281383</v>
+        <v>3.794548191502888</v>
       </c>
     </row>
     <row r="523">
@@ -21884,7 +21884,7 @@
         <v>8</v>
       </c>
       <c r="K523" t="n">
-        <v>3.795105184281383</v>
+        <v>3.794548191502888</v>
       </c>
     </row>
     <row r="524">
@@ -21925,7 +21925,7 @@
         <v>8</v>
       </c>
       <c r="K524" t="n">
-        <v>3.785935884333672</v>
+        <v>3.786818822964201</v>
       </c>
     </row>
     <row r="525">
@@ -21966,7 +21966,7 @@
         <v>8</v>
       </c>
       <c r="K525" t="n">
-        <v>3.747036503155814</v>
+        <v>3.749713034293163</v>
       </c>
     </row>
     <row r="526">
@@ -22007,7 +22007,7 @@
         <v>8</v>
       </c>
       <c r="K526" t="n">
-        <v>3.719584165492087</v>
+        <v>3.718202302502333</v>
       </c>
     </row>
     <row r="527">
@@ -22048,7 +22048,7 @@
         <v>8</v>
       </c>
       <c r="K527" t="n">
-        <v>3.719584165492087</v>
+        <v>3.718202302502333</v>
       </c>
     </row>
     <row r="528">
@@ -22089,7 +22089,7 @@
         <v>8</v>
       </c>
       <c r="K528" t="n">
-        <v>3.753807040736591</v>
+        <v>3.750490607473395</v>
       </c>
     </row>
     <row r="529">
@@ -22130,7 +22130,7 @@
         <v>8</v>
       </c>
       <c r="K529" t="n">
-        <v>3.789620036406627</v>
+        <v>3.786342706920184</v>
       </c>
     </row>
     <row r="530">
@@ -22171,7 +22171,7 @@
         <v>8</v>
       </c>
       <c r="K530" t="n">
-        <v>3.789620036406627</v>
+        <v>3.821450994894537</v>
       </c>
     </row>
     <row r="531">
@@ -22212,7 +22212,7 @@
         <v>8</v>
       </c>
       <c r="K531" t="n">
-        <v>3.789620036406627</v>
+        <v>3.821450994894537</v>
       </c>
     </row>
     <row r="532">
@@ -22253,7 +22253,7 @@
         <v>8</v>
       </c>
       <c r="K532" t="n">
-        <v>3.854710098713524</v>
+        <v>3.853244781667679</v>
       </c>
     </row>
     <row r="533">
@@ -22294,7 +22294,7 @@
         <v>8</v>
       </c>
       <c r="K533" t="n">
-        <v>3.811336742547534</v>
+        <v>3.811411436453454</v>
       </c>
     </row>
     <row r="534">
@@ -22335,7 +22335,7 @@
         <v>8</v>
       </c>
       <c r="K534" t="n">
-        <v>3.811336742547534</v>
+        <v>3.811411436453454</v>
       </c>
     </row>
     <row r="535">
@@ -22376,7 +22376,7 @@
         <v>8</v>
       </c>
       <c r="K535" t="n">
-        <v>3.801400452720887</v>
+        <v>3.802113649195304</v>
       </c>
     </row>
     <row r="536">
@@ -22417,7 +22417,7 @@
         <v>8</v>
       </c>
       <c r="K536" t="n">
-        <v>3.801400452720887</v>
+        <v>3.802113649195304</v>
       </c>
     </row>
     <row r="537">
@@ -22458,7 +22458,7 @@
         <v>8</v>
       </c>
       <c r="K537" t="n">
-        <v>3.801400452720887</v>
+        <v>3.802113649195304</v>
       </c>
     </row>
     <row r="538">
@@ -22499,7 +22499,7 @@
         <v>8</v>
       </c>
       <c r="K538" t="n">
-        <v>3.801400452720887</v>
+        <v>3.802113649195304</v>
       </c>
     </row>
     <row r="539">
@@ -22540,7 +22540,7 @@
         <v>8</v>
       </c>
       <c r="K539" t="n">
-        <v>3.801400452720887</v>
+        <v>3.802113649195304</v>
       </c>
     </row>
     <row r="540">
@@ -22581,7 +22581,7 @@
         <v>8</v>
       </c>
       <c r="K540" t="n">
-        <v>3.847183931065179</v>
+        <v>3.843130659089398</v>
       </c>
     </row>
     <row r="541">
@@ -22622,7 +22622,7 @@
         <v>8</v>
       </c>
       <c r="K541" t="n">
-        <v>3.847183931065179</v>
+        <v>3.843130659089398</v>
       </c>
     </row>
     <row r="542">
@@ -22663,7 +22663,7 @@
         <v>8</v>
       </c>
       <c r="K542" t="n">
-        <v>3.9129405295598</v>
+        <v>3.909818655273012</v>
       </c>
     </row>
     <row r="543">
@@ -22704,7 +22704,7 @@
         <v>8</v>
       </c>
       <c r="K543" t="n">
-        <v>3.941885751107199</v>
+        <v>3.939164528454642</v>
       </c>
     </row>
     <row r="544">
@@ -22745,7 +22745,7 @@
         <v>8</v>
       </c>
       <c r="K544" t="n">
-        <v>4.222231765800755</v>
+        <v>4.205404230369973</v>
       </c>
     </row>
     <row r="545">
@@ -22786,7 +22786,7 @@
         <v>8</v>
       </c>
       <c r="K545" t="n">
-        <v>4.298044307236188</v>
+        <v>4.286004068946803</v>
       </c>
     </row>
     <row r="546">
@@ -22827,7 +22827,7 @@
         <v>8</v>
       </c>
       <c r="K546" t="n">
-        <v>4.298044307236188</v>
+        <v>4.286004068946803</v>
       </c>
     </row>
     <row r="547">
@@ -22868,7 +22868,7 @@
         <v>8</v>
       </c>
       <c r="K547" t="n">
-        <v>4.298044307236188</v>
+        <v>4.286004068946803</v>
       </c>
     </row>
     <row r="548">
@@ -22909,7 +22909,7 @@
         <v>8</v>
       </c>
       <c r="K548" t="n">
-        <v>4.34641166674113</v>
+        <v>4.343511447221824</v>
       </c>
     </row>
     <row r="549">
@@ -22950,7 +22950,7 @@
         <v>8</v>
       </c>
       <c r="K549" t="n">
-        <v>4.399143297440226</v>
+        <v>4.40025266548828</v>
       </c>
     </row>
     <row r="550">
@@ -22991,7 +22991,7 @@
         <v>8</v>
       </c>
       <c r="K550" t="n">
-        <v>4.499565967367278</v>
+        <v>4.497174995519615</v>
       </c>
     </row>
     <row r="551">
@@ -23032,7 +23032,7 @@
         <v>8</v>
       </c>
       <c r="K551" t="n">
-        <v>4.607003251161557</v>
+        <v>4.573939241293859</v>
       </c>
     </row>
     <row r="552">
@@ -23073,7 +23073,7 @@
         <v>8</v>
       </c>
       <c r="K552" t="n">
-        <v>4.500201022009525</v>
+        <v>4.50684168661622</v>
       </c>
     </row>
     <row r="553">
@@ -23114,7 +23114,7 @@
         <v>8</v>
       </c>
       <c r="K553" t="n">
-        <v>4.500201022009525</v>
+        <v>4.50684168661622</v>
       </c>
     </row>
     <row r="554">
@@ -23155,7 +23155,7 @@
         <v>8</v>
       </c>
       <c r="K554" t="n">
-        <v>4.500201022009525</v>
+        <v>4.50684168661622</v>
       </c>
     </row>
     <row r="555">
@@ -23196,7 +23196,7 @@
         <v>8</v>
       </c>
       <c r="K555" t="n">
-        <v>4.161968355189815</v>
+        <v>4.169138391629663</v>
       </c>
     </row>
     <row r="556">
@@ -23237,7 +23237,7 @@
         <v>8</v>
       </c>
       <c r="K556" t="n">
-        <v>4.079054854107293</v>
+        <v>4.086506876279971</v>
       </c>
     </row>
     <row r="557">
@@ -23278,7 +23278,7 @@
         <v>8</v>
       </c>
       <c r="K557" t="n">
-        <v>3.89873811658448</v>
+        <v>3.907049327490454</v>
       </c>
     </row>
     <row r="558">
@@ -23319,7 +23319,7 @@
         <v>8</v>
       </c>
       <c r="K558" t="n">
-        <v>3.686925755888744</v>
+        <v>3.696501827403492</v>
       </c>
     </row>
     <row r="559">
@@ -23360,7 +23360,7 @@
         <v>8</v>
       </c>
       <c r="K559" t="n">
-        <v>3.686925755888744</v>
+        <v>3.63667776618289</v>
       </c>
     </row>
     <row r="560">
@@ -23401,7 +23401,7 @@
         <v>8</v>
       </c>
       <c r="K560" t="n">
-        <v>3.599469139312606</v>
+        <v>3.602367933577699</v>
       </c>
     </row>
     <row r="561">
@@ -23442,7 +23442,7 @@
         <v>8</v>
       </c>
       <c r="K561" t="n">
-        <v>3.574906299407029</v>
+        <v>3.575844641807014</v>
       </c>
     </row>
     <row r="562">
@@ -23483,7 +23483,7 @@
         <v>8</v>
       </c>
       <c r="K562" t="n">
-        <v>3.574906299407029</v>
+        <v>3.575844641807014</v>
       </c>
     </row>
     <row r="563">
@@ -23524,7 +23524,7 @@
         <v>8</v>
       </c>
       <c r="K563" t="n">
-        <v>3.56026612717393</v>
+        <v>3.561585808630114</v>
       </c>
     </row>
     <row r="564">
@@ -23565,7 +23565,7 @@
         <v>8</v>
       </c>
       <c r="K564" t="n">
-        <v>3.513890299194632</v>
+        <v>3.516487320896461</v>
       </c>
     </row>
     <row r="565">
@@ -23606,7 +23606,7 @@
         <v>8</v>
       </c>
       <c r="K565" t="n">
-        <v>3.483229171038073</v>
+        <v>3.486286381778102</v>
       </c>
     </row>
     <row r="566">
@@ -23647,7 +23647,7 @@
         <v>8</v>
       </c>
       <c r="K566" t="n">
-        <v>3.458208653829165</v>
+        <v>3.460628072577304</v>
       </c>
     </row>
     <row r="567">
@@ -23688,7 +23688,7 @@
         <v>8</v>
       </c>
       <c r="K567" t="n">
-        <v>3.458208653829165</v>
+        <v>3.460628072577304</v>
       </c>
     </row>
     <row r="568">
@@ -23729,7 +23729,7 @@
         <v>8</v>
       </c>
       <c r="K568" t="n">
-        <v>3.458208653829165</v>
+        <v>3.460628072577304</v>
       </c>
     </row>
     <row r="569">
@@ -23770,7 +23770,7 @@
         <v>8</v>
       </c>
       <c r="K569" t="n">
-        <v>3.377991407020929</v>
+        <v>3.379048560066597</v>
       </c>
     </row>
     <row r="570">
@@ -23811,7 +23811,7 @@
         <v>8</v>
       </c>
       <c r="K570" t="n">
-        <v>3.377991407020929</v>
+        <v>3.335278728837551</v>
       </c>
     </row>
     <row r="571">
@@ -23852,7 +23852,7 @@
         <v>8</v>
       </c>
       <c r="K571" t="n">
-        <v>3.254621292464293</v>
+        <v>3.256768616796267</v>
       </c>
     </row>
     <row r="572">
@@ -23893,7 +23893,7 @@
         <v>8</v>
       </c>
       <c r="K572" t="n">
-        <v>3.164508761283598</v>
+        <v>3.166633725876596</v>
       </c>
     </row>
     <row r="573">
@@ -23934,7 +23934,7 @@
         <v>8</v>
       </c>
       <c r="K573" t="n">
-        <v>3.142659355577249</v>
+        <v>3.144407768060876</v>
       </c>
     </row>
     <row r="574">
@@ -23975,7 +23975,7 @@
         <v>8</v>
       </c>
       <c r="K574" t="n">
-        <v>3.107477070793768</v>
+        <v>3.109428386925875</v>
       </c>
     </row>
     <row r="575">
@@ -24016,7 +24016,7 @@
         <v>8</v>
       </c>
       <c r="K575" t="n">
-        <v>3.093479049614354</v>
+        <v>3.093899460791998</v>
       </c>
     </row>
     <row r="576">
@@ -24057,7 +24057,7 @@
         <v>8</v>
       </c>
       <c r="K576" t="n">
-        <v>3.097011467126507</v>
+        <v>3.095860365737547</v>
       </c>
     </row>
     <row r="577">
@@ -24098,7 +24098,7 @@
         <v>8</v>
       </c>
       <c r="K577" t="n">
-        <v>3.361929980736655</v>
+        <v>3.354391134194454</v>
       </c>
     </row>
     <row r="578">
@@ -24139,7 +24139,7 @@
         <v>8</v>
       </c>
       <c r="K578" t="n">
-        <v>3.516997251485912</v>
+        <v>3.510187341933805</v>
       </c>
     </row>
     <row r="579">
@@ -24180,7 +24180,7 @@
         <v>8</v>
       </c>
       <c r="K579" t="n">
-        <v>3.592487847178353</v>
+        <v>3.655519493520329</v>
       </c>
     </row>
     <row r="580">
@@ -24221,7 +24221,7 @@
         <v>8</v>
       </c>
       <c r="K580" t="n">
-        <v>3.720900916533644</v>
+        <v>3.715563852803498</v>
       </c>
     </row>
     <row r="581">
@@ -24262,7 +24262,7 @@
         <v>8</v>
       </c>
       <c r="K581" t="n">
-        <v>3.828878641252579</v>
+        <v>3.824424776309838</v>
       </c>
     </row>
     <row r="582">
@@ -24303,7 +24303,7 @@
         <v>8</v>
       </c>
       <c r="K582" t="n">
-        <v>3.828878641252579</v>
+        <v>3.824424776309838</v>
       </c>
     </row>
     <row r="583">
@@ -24344,7 +24344,7 @@
         <v>8</v>
       </c>
       <c r="K583" t="n">
-        <v>3.869726942198543</v>
+        <v>3.866603237050137</v>
       </c>
     </row>
     <row r="584">
@@ -24385,7 +24385,7 @@
         <v>8</v>
       </c>
       <c r="K584" t="n">
-        <v>3.745523852194593</v>
+        <v>3.677029310359428</v>
       </c>
     </row>
     <row r="585">
@@ -24426,7 +24426,7 @@
         <v>8</v>
       </c>
       <c r="K585" t="n">
-        <v>3.590664440185916</v>
+        <v>3.597972044156936</v>
       </c>
     </row>
     <row r="586">
@@ -24467,7 +24467,7 @@
         <v>8</v>
       </c>
       <c r="K586" t="n">
-        <v>3.297845997558641</v>
+        <v>3.302919550911891</v>
       </c>
     </row>
     <row r="587">
@@ -24508,7 +24508,7 @@
         <v>8</v>
       </c>
       <c r="K587" t="n">
-        <v>3.255284721501393</v>
+        <v>3.258113800560746</v>
       </c>
     </row>
     <row r="588">
@@ -24549,7 +24549,7 @@
         <v>8</v>
       </c>
       <c r="K588" t="n">
-        <v>3.249067936813264</v>
+        <v>3.249320662502178</v>
       </c>
     </row>
     <row r="589">
@@ -24590,7 +24590,7 @@
         <v>8</v>
       </c>
       <c r="K589" t="n">
-        <v>3.276041087894209</v>
+        <v>3.273611588769174</v>
       </c>
     </row>
     <row r="590">
@@ -24631,7 +24631,7 @@
         <v>8</v>
       </c>
       <c r="K590" t="n">
-        <v>3.276041087894209</v>
+        <v>3.298849852583644</v>
       </c>
     </row>
     <row r="591">
@@ -24672,7 +24672,7 @@
         <v>8</v>
       </c>
       <c r="K591" t="n">
-        <v>3.346330796481479</v>
+        <v>3.344690668747884</v>
       </c>
     </row>
     <row r="592">
@@ -24713,7 +24713,7 @@
         <v>8</v>
       </c>
       <c r="K592" t="n">
-        <v>3.357377241765973</v>
+        <v>3.356719147888827</v>
       </c>
     </row>
     <row r="593">
@@ -24754,7 +24754,7 @@
         <v>8</v>
       </c>
       <c r="K593" t="n">
-        <v>3.365753957185158</v>
+        <v>3.366324754876798</v>
       </c>
     </row>
     <row r="594">
@@ -24795,7 +24795,7 @@
         <v>8</v>
       </c>
       <c r="K594" t="n">
-        <v>3.365976286001511</v>
+        <v>3.366324754876798</v>
       </c>
     </row>
     <row r="595">
@@ -24836,7 +24836,7 @@
         <v>8</v>
       </c>
       <c r="K595" t="n">
-        <v>3.349936432469709</v>
+        <v>3.350955197055436</v>
       </c>
     </row>
     <row r="596">
@@ -24877,7 +24877,7 @@
         <v>8</v>
       </c>
       <c r="K596" t="n">
-        <v>3.340804689623056</v>
+        <v>3.34162294258718</v>
       </c>
     </row>
     <row r="597">
@@ -24918,7 +24918,7 @@
         <v>8</v>
       </c>
       <c r="K597" t="n">
-        <v>3.330627315386018</v>
+        <v>3.331628067015555</v>
       </c>
     </row>
     <row r="598">
@@ -24959,7 +24959,7 @@
         <v>8</v>
       </c>
       <c r="K598" t="n">
-        <v>3.330627315386018</v>
+        <v>3.331628067015555</v>
       </c>
     </row>
     <row r="599">
@@ -25000,7 +25000,7 @@
         <v>8</v>
       </c>
       <c r="K599" t="n">
-        <v>3.318746959718221</v>
+        <v>3.320887546096086</v>
       </c>
     </row>
     <row r="600">
@@ -25041,7 +25041,7 @@
         <v>8</v>
       </c>
       <c r="K600" t="n">
-        <v>3.290861319644303</v>
+        <v>3.293592476068977</v>
       </c>
     </row>
     <row r="601">
@@ -25082,7 +25082,7 @@
         <v>8</v>
       </c>
       <c r="K601" t="n">
-        <v>3.262218781231735</v>
+        <v>3.242754774372556</v>
       </c>
     </row>
     <row r="602">
@@ -25123,7 +25123,7 @@
         <v>8</v>
       </c>
       <c r="K602" t="n">
-        <v>3.24064369222713</v>
+        <v>3.242754774372556</v>
       </c>
     </row>
     <row r="603">
@@ -25164,7 +25164,7 @@
         <v>8</v>
       </c>
       <c r="K603" t="n">
-        <v>3.161021172326477</v>
+        <v>3.163831755628244</v>
       </c>
     </row>
     <row r="604">
@@ -25205,7 +25205,7 @@
         <v>8</v>
       </c>
       <c r="K604" t="n">
-        <v>3.161021172326477</v>
+        <v>3.13022937180194</v>
       </c>
     </row>
     <row r="605">
@@ -25246,7 +25246,7 @@
         <v>8</v>
       </c>
       <c r="K605" t="n">
-        <v>3.125613886959688</v>
+        <v>3.072009873383873</v>
       </c>
     </row>
     <row r="606">
@@ -25287,7 +25287,7 @@
         <v>8</v>
       </c>
       <c r="K606" t="n">
-        <v>3.010804360263628</v>
+        <v>3.012906479458919</v>
       </c>
     </row>
     <row r="607">
@@ -25328,7 +25328,7 @@
         <v>8</v>
       </c>
       <c r="K607" t="n">
-        <v>3.116796064583831</v>
+        <v>3.113068261438969</v>
       </c>
     </row>
     <row r="608">
@@ -25369,7 +25369,7 @@
         <v>8</v>
       </c>
       <c r="K608" t="n">
-        <v>3.116796064583831</v>
+        <v>3.113068261438969</v>
       </c>
     </row>
     <row r="609">
@@ -25410,7 +25410,7 @@
         <v>8</v>
       </c>
       <c r="K609" t="n">
-        <v>3.177070607628845</v>
+        <v>3.179633196657701</v>
       </c>
     </row>
     <row r="610">
@@ -25451,7 +25451,7 @@
         <v>8</v>
       </c>
       <c r="K610" t="n">
-        <v>3.177070607628845</v>
+        <v>3.179633196657701</v>
       </c>
     </row>
     <row r="611">
@@ -25492,7 +25492,7 @@
         <v>8</v>
       </c>
       <c r="K611" t="n">
-        <v>3.141049778860678</v>
+        <v>3.145384371912646</v>
       </c>
     </row>
     <row r="612">
@@ -25533,7 +25533,7 @@
         <v>8</v>
       </c>
       <c r="K612" t="n">
-        <v>3.090364929859494</v>
+        <v>3.095476021472693</v>
       </c>
     </row>
     <row r="613">
@@ -25574,7 +25574,7 @@
         <v>8</v>
       </c>
       <c r="K613" t="n">
-        <v>2.983559293170533</v>
+        <v>2.989370259205931</v>
       </c>
     </row>
     <row r="614">
@@ -25615,7 +25615,7 @@
         <v>8</v>
       </c>
       <c r="K614" t="n">
-        <v>2.931760514729453</v>
+        <v>2.936301206845917</v>
       </c>
     </row>
     <row r="615">
@@ -25656,7 +25656,7 @@
         <v>8</v>
       </c>
       <c r="K615" t="n">
-        <v>2.890591283514847</v>
+        <v>2.895138521073013</v>
       </c>
     </row>
     <row r="616">
@@ -25697,7 +25697,7 @@
         <v>8</v>
       </c>
       <c r="K616" t="n">
-        <v>2.793387800468718</v>
+        <v>2.798492958601614</v>
       </c>
     </row>
     <row r="617">
@@ -25738,7 +25738,7 @@
         <v>8</v>
       </c>
       <c r="K617" t="n">
-        <v>2.747555390777777</v>
+        <v>2.752215590021334</v>
       </c>
     </row>
     <row r="618">
@@ -25779,7 +25779,7 @@
         <v>8</v>
       </c>
       <c r="K618" t="n">
-        <v>2.747555390777777</v>
+        <v>2.752215590021334</v>
       </c>
     </row>
     <row r="619">
@@ -25820,7 +25820,7 @@
         <v>8</v>
       </c>
       <c r="K619" t="n">
-        <v>2.657952815611732</v>
+        <v>2.663461105614243</v>
       </c>
     </row>
     <row r="620">
@@ -25861,7 +25861,7 @@
         <v>8</v>
       </c>
       <c r="K620" t="n">
-        <v>2.603781704502235</v>
+        <v>2.609259349720502</v>
       </c>
     </row>
     <row r="621">
@@ -25902,7 +25902,7 @@
         <v>8</v>
       </c>
       <c r="K621" t="n">
-        <v>2.572214564677665</v>
+        <v>2.570747856752329</v>
       </c>
     </row>
     <row r="622">
@@ -25943,7 +25943,7 @@
         <v>8</v>
       </c>
       <c r="K622" t="n">
-        <v>2.580087565102579</v>
+        <v>2.579860026721035</v>
       </c>
     </row>
     <row r="623">
@@ -25984,7 +25984,7 @@
         <v>8</v>
       </c>
       <c r="K623" t="n">
-        <v>2.580087565102579</v>
+        <v>2.579860026721035</v>
       </c>
     </row>
     <row r="624">
@@ -26025,7 +26025,7 @@
         <v>8</v>
       </c>
       <c r="K624" t="n">
-        <v>2.529208667340332</v>
+        <v>2.517161497336506</v>
       </c>
     </row>
     <row r="625">
@@ -26066,7 +26066,7 @@
         <v>8</v>
       </c>
       <c r="K625" t="n">
-        <v>2.515885689444435</v>
+        <v>2.517161497336506</v>
       </c>
     </row>
     <row r="626">
@@ -26107,7 +26107,7 @@
         <v>8</v>
       </c>
       <c r="K626" t="n">
-        <v>2.515885689444435</v>
+        <v>2.517161497336506</v>
       </c>
     </row>
     <row r="627">
@@ -26148,7 +26148,7 @@
         <v>8</v>
       </c>
       <c r="K627" t="n">
-        <v>2.515885689444435</v>
+        <v>2.501697532094298</v>
       </c>
     </row>
     <row r="628">
@@ -26189,7 +26189,7 @@
         <v>8</v>
       </c>
       <c r="K628" t="n">
-        <v>2.498675732113951</v>
+        <v>2.501697532094298</v>
       </c>
     </row>
     <row r="629">
@@ -26230,7 +26230,7 @@
         <v>8</v>
       </c>
       <c r="K629" t="n">
-        <v>2.400259861084353</v>
+        <v>2.403351000044303</v>
       </c>
     </row>
     <row r="630">
@@ -26271,7 +26271,7 @@
         <v>8</v>
       </c>
       <c r="K630" t="n">
-        <v>2.367863269247264</v>
+        <v>2.371569357596123</v>
       </c>
     </row>
     <row r="631">
@@ -26312,7 +26312,7 @@
         <v>8</v>
       </c>
       <c r="K631" t="n">
-        <v>2.339021693161395</v>
+        <v>2.342359792538077</v>
       </c>
     </row>
     <row r="632">
@@ -26353,7 +26353,7 @@
         <v>8</v>
       </c>
       <c r="K632" t="n">
-        <v>2.339021693161395</v>
+        <v>2.342359792538077</v>
       </c>
     </row>
     <row r="633">
@@ -26394,7 +26394,7 @@
         <v>8</v>
       </c>
       <c r="K633" t="n">
-        <v>2.285212181445828</v>
+        <v>2.224461001062489</v>
       </c>
     </row>
     <row r="634">
@@ -26435,7 +26435,7 @@
         <v>8</v>
       </c>
       <c r="K634" t="n">
-        <v>2.216465470948244</v>
+        <v>2.224461001062489</v>
       </c>
     </row>
     <row r="635">
@@ -26476,7 +26476,7 @@
         <v>8</v>
       </c>
       <c r="K635" t="n">
-        <v>2.156744632485166</v>
+        <v>2.162334352411885</v>
       </c>
     </row>
     <row r="636">
@@ -26517,7 +26517,7 @@
         <v>8</v>
       </c>
       <c r="K636" t="n">
-        <v>2.109493577764023</v>
+        <v>2.114753784772394</v>
       </c>
     </row>
     <row r="637">
@@ -26558,7 +26558,7 @@
         <v>8</v>
       </c>
       <c r="K637" t="n">
-        <v>2.094605406568965</v>
+        <v>2.09015932976187</v>
       </c>
     </row>
     <row r="638">
@@ -26599,7 +26599,7 @@
         <v>8</v>
       </c>
       <c r="K638" t="n">
-        <v>2.094605406568965</v>
+        <v>2.09015932976187</v>
       </c>
     </row>
     <row r="639">
@@ -26640,7 +26640,7 @@
         <v>8</v>
       </c>
       <c r="K639" t="n">
-        <v>2.094605406568965</v>
+        <v>2.127388724604658</v>
       </c>
     </row>
     <row r="640">
@@ -26681,7 +26681,7 @@
         <v>8</v>
       </c>
       <c r="K640" t="n">
-        <v>2.237623414749074</v>
+        <v>2.231635421861665</v>
       </c>
     </row>
     <row r="641">
@@ -26722,7 +26722,7 @@
         <v>8</v>
       </c>
       <c r="K641" t="n">
-        <v>2.237623414749074</v>
+        <v>2.231635421861665</v>
       </c>
     </row>
     <row r="642">
@@ -26763,7 +26763,7 @@
         <v>8</v>
       </c>
       <c r="K642" t="n">
-        <v>2.291464611014832</v>
+        <v>2.328098827141243</v>
       </c>
     </row>
     <row r="643">
@@ -26804,7 +26804,7 @@
         <v>8</v>
       </c>
       <c r="K643" t="n">
-        <v>2.357334692006394</v>
+        <v>2.350233553670546</v>
       </c>
     </row>
     <row r="644">
@@ -26845,7 +26845,7 @@
         <v>8</v>
       </c>
       <c r="K644" t="n">
-        <v>2.346104625397664</v>
+        <v>2.316966410452066</v>
       </c>
     </row>
     <row r="645">
@@ -26886,7 +26886,7 @@
         <v>8</v>
       </c>
       <c r="K645" t="n">
-        <v>2.316495350626875</v>
+        <v>2.316966410452066</v>
       </c>
     </row>
     <row r="646">
@@ -26927,7 +26927,7 @@
         <v>8</v>
       </c>
       <c r="K646" t="n">
-        <v>2.316495350626875</v>
+        <v>2.316966410452066</v>
       </c>
     </row>
     <row r="647">
@@ -26968,7 +26968,7 @@
         <v>8</v>
       </c>
       <c r="K647" t="n">
-        <v>2.208624778372181</v>
+        <v>2.210538049288024</v>
       </c>
     </row>
     <row r="648">
@@ -27009,7 +27009,7 @@
         <v>8</v>
       </c>
       <c r="K648" t="n">
-        <v>2.152667487832997</v>
+        <v>2.155726120229029</v>
       </c>
     </row>
     <row r="649">
@@ -27050,7 +27050,7 @@
         <v>8</v>
       </c>
       <c r="K649" t="n">
-        <v>1.980933041059145</v>
+        <v>1.985389346273891</v>
       </c>
     </row>
     <row r="650">
@@ -27091,7 +27091,7 @@
         <v>8</v>
       </c>
       <c r="K650" t="n">
-        <v>1.849005593652235</v>
+        <v>1.849024802614025</v>
       </c>
     </row>
     <row r="651">
@@ -27132,7 +27132,7 @@
         <v>8</v>
       </c>
       <c r="K651" t="n">
-        <v>1.854752817349508</v>
+        <v>1.854330248067195</v>
       </c>
     </row>
     <row r="652">
@@ -27173,7 +27173,7 @@
         <v>8</v>
       </c>
       <c r="K652" t="n">
-        <v>1.861627467005655</v>
+        <v>1.861095154736198</v>
       </c>
     </row>
     <row r="653">
@@ -27214,7 +27214,7 @@
         <v>8</v>
       </c>
       <c r="K653" t="n">
-        <v>2.260557242222242</v>
+        <v>2.248510279827753</v>
       </c>
     </row>
     <row r="654">
@@ -27255,7 +27255,7 @@
         <v>8</v>
       </c>
       <c r="K654" t="n">
-        <v>2.260557242222242</v>
+        <v>2.248510279827753</v>
       </c>
     </row>
     <row r="655">
@@ -27296,7 +27296,7 @@
         <v>8</v>
       </c>
       <c r="K655" t="n">
-        <v>2.71442678617928</v>
+        <v>2.70251102389674</v>
       </c>
     </row>
     <row r="656">
@@ -27337,7 +27337,7 @@
         <v>8</v>
       </c>
       <c r="K656" t="n">
-        <v>2.995901487791957</v>
+        <v>2.985419836488866</v>
       </c>
     </row>
     <row r="657">
@@ -27378,7 +27378,7 @@
         <v>8</v>
       </c>
       <c r="K657" t="n">
-        <v>3.241949999485116</v>
+        <v>3.232029763099373</v>
       </c>
     </row>
     <row r="658">
@@ -27419,7 +27419,7 @@
         <v>8</v>
       </c>
       <c r="K658" t="n">
-        <v>3.492052559738734</v>
+        <v>3.48884804463409</v>
       </c>
     </row>
     <row r="659">
@@ -27460,7 +27460,7 @@
         <v>8</v>
       </c>
       <c r="K659" t="n">
-        <v>3.530572751906444</v>
+        <v>3.527549909470098</v>
       </c>
     </row>
     <row r="660">
@@ -27501,7 +27501,7 @@
         <v>8</v>
       </c>
       <c r="K660" t="n">
-        <v>3.554505891845775</v>
+        <v>3.556687488909232</v>
       </c>
     </row>
     <row r="661">
@@ -27542,7 +27542,7 @@
         <v>8</v>
       </c>
       <c r="K661" t="n">
-        <v>3.524258726588451</v>
+        <v>3.526909644047683</v>
       </c>
     </row>
     <row r="662">
@@ -27583,7 +27583,7 @@
         <v>8</v>
       </c>
       <c r="K662" t="n">
-        <v>3.414061633697127</v>
+        <v>3.421224496007529</v>
       </c>
     </row>
     <row r="663">
@@ -27624,7 +27624,7 @@
         <v>8</v>
       </c>
       <c r="K663" t="n">
-        <v>3.083832766773205</v>
+        <v>3.094029361087061</v>
       </c>
     </row>
     <row r="664">
@@ -27665,7 +27665,7 @@
         <v>8</v>
       </c>
       <c r="K664" t="n">
-        <v>2.698465521488344</v>
+        <v>2.705756900936824</v>
       </c>
     </row>
     <row r="665">
@@ -27706,7 +27706,7 @@
         <v>8</v>
       </c>
       <c r="K665" t="n">
-        <v>2.698465521488344</v>
+        <v>2.626119279190886</v>
       </c>
     </row>
     <row r="666">
@@ -27747,7 +27747,7 @@
         <v>8</v>
       </c>
       <c r="K666" t="n">
-        <v>2.546069297054327</v>
+        <v>2.552882908917801</v>
       </c>
     </row>
     <row r="667">
@@ -27788,7 +27788,7 @@
         <v>8</v>
       </c>
       <c r="K667" t="n">
-        <v>2.455877889758174</v>
+        <v>2.464337492827533</v>
       </c>
     </row>
     <row r="668">
@@ -27829,7 +27829,7 @@
         <v>8</v>
       </c>
       <c r="K668" t="n">
-        <v>2.359044657744962</v>
+        <v>2.367170843466984</v>
       </c>
     </row>
     <row r="669">
@@ -27870,7 +27870,7 @@
         <v>8</v>
       </c>
       <c r="K669" t="n">
-        <v>2.270396531913014</v>
+        <v>2.27794077037484</v>
       </c>
     </row>
     <row r="670">
@@ -27911,7 +27911,7 @@
         <v>8</v>
       </c>
       <c r="K670" t="n">
-        <v>2.270396531913014</v>
+        <v>2.192299314189107</v>
       </c>
     </row>
     <row r="671">
@@ -27952,7 +27952,7 @@
         <v>8</v>
       </c>
       <c r="K671" t="n">
-        <v>2.184523311939132</v>
+        <v>2.090485416501012</v>
       </c>
     </row>
     <row r="672">
@@ -27993,7 +27993,7 @@
         <v>8</v>
       </c>
       <c r="K672" t="n">
-        <v>2.081349647047166</v>
+        <v>2.090485416501012</v>
       </c>
     </row>
     <row r="673">
@@ -28034,7 +28034,7 @@
         <v>8</v>
       </c>
       <c r="K673" t="n">
-        <v>1.908878638891737</v>
+        <v>1.916274347808392</v>
       </c>
     </row>
     <row r="674">
@@ -28075,7 +28075,7 @@
         <v>8</v>
       </c>
       <c r="K674" t="n">
-        <v>1.822419946767903</v>
+        <v>1.830377717594008</v>
       </c>
     </row>
     <row r="675">
@@ -28116,7 +28116,7 @@
         <v>8</v>
       </c>
       <c r="K675" t="n">
-        <v>1.822419946767903</v>
+        <v>1.830377717594008</v>
       </c>
     </row>
     <row r="676">
@@ -28157,7 +28157,7 @@
         <v>8</v>
       </c>
       <c r="K676" t="n">
-        <v>1.509746427872291</v>
+        <v>1.515269151778716</v>
       </c>
     </row>
     <row r="677">
@@ -28198,7 +28198,7 @@
         <v>8</v>
       </c>
       <c r="K677" t="n">
-        <v>1.380663490793484</v>
+        <v>1.386567271684889</v>
       </c>
     </row>
     <row r="678">
@@ -28239,7 +28239,7 @@
         <v>8</v>
       </c>
       <c r="K678" t="n">
-        <v>1.311154953600703</v>
+        <v>1.317821297786809</v>
       </c>
     </row>
     <row r="679">
@@ -28280,7 +28280,7 @@
         <v>8</v>
       </c>
       <c r="K679" t="n">
-        <v>1.121698848909578</v>
+        <v>1.133199797692549</v>
       </c>
     </row>
     <row r="680">
@@ -28321,7 +28321,7 @@
         <v>8</v>
       </c>
       <c r="K680" t="n">
-        <v>0.8531202425542674</v>
+        <v>0.8584192825517314</v>
       </c>
     </row>
     <row r="681">
@@ -28362,7 +28362,7 @@
         <v>8</v>
       </c>
       <c r="K681" t="n">
-        <v>0.8531202425542674</v>
+        <v>0.8584192825517314</v>
       </c>
     </row>
     <row r="682">
@@ -28403,7 +28403,7 @@
         <v>8</v>
       </c>
       <c r="K682" t="n">
-        <v>0.7588240922124914</v>
+        <v>0.7628558720518619</v>
       </c>
     </row>
     <row r="683">
@@ -28444,7 +28444,7 @@
         <v>8</v>
       </c>
       <c r="K683" t="n">
-        <v>0.9074749682454487</v>
+        <v>0.9003591654609713</v>
       </c>
     </row>
     <row r="684">
@@ -28485,7 +28485,7 @@
         <v>8</v>
       </c>
       <c r="K684" t="n">
-        <v>1.070464306901245</v>
+        <v>1.06231017256995</v>
       </c>
     </row>
     <row r="685">
@@ -28526,7 +28526,7 @@
         <v>8</v>
       </c>
       <c r="K685" t="n">
-        <v>1.156656760048637</v>
+        <v>1.148985115409826</v>
       </c>
     </row>
     <row r="686">
@@ -28567,7 +28567,7 @@
         <v>8</v>
       </c>
       <c r="K686" t="n">
-        <v>1.246681586703326</v>
+        <v>1.237576952663011</v>
       </c>
     </row>
     <row r="687">
@@ -28608,7 +28608,7 @@
         <v>8</v>
       </c>
       <c r="K687" t="n">
-        <v>1.476857695308993</v>
+        <v>1.464972328382154</v>
       </c>
     </row>
     <row r="688">
@@ -28649,7 +28649,7 @@
         <v>8</v>
       </c>
       <c r="K688" t="n">
-        <v>1.678182818765495</v>
+        <v>1.670020895061193</v>
       </c>
     </row>
     <row r="689">
@@ -28690,7 +28690,7 @@
         <v>8</v>
       </c>
       <c r="K689" t="n">
-        <v>1.749437365865393</v>
+        <v>1.743803522199769</v>
       </c>
     </row>
     <row r="690">
@@ -28731,7 +28731,7 @@
         <v>8</v>
       </c>
       <c r="K690" t="n">
-        <v>1.749437365865393</v>
+        <v>1.743803522199769</v>
       </c>
     </row>
     <row r="691">
@@ -28772,7 +28772,7 @@
         <v>8</v>
       </c>
       <c r="K691" t="n">
-        <v>1.741445779746115</v>
+        <v>1.741838298508129</v>
       </c>
     </row>
     <row r="692">
@@ -28813,7 +28813,7 @@
         <v>8</v>
       </c>
       <c r="K692" t="n">
-        <v>1.741445779746115</v>
+        <v>1.741838298508129</v>
       </c>
     </row>
     <row r="693">
@@ -28854,7 +28854,7 @@
         <v>8</v>
       </c>
       <c r="K693" t="n">
-        <v>1.801851371956483</v>
+        <v>1.800076749635754</v>
       </c>
     </row>
     <row r="694">
@@ -28895,7 +28895,7 @@
         <v>8</v>
       </c>
       <c r="K694" t="n">
-        <v>1.801851371956483</v>
+        <v>1.800076749635754</v>
       </c>
     </row>
     <row r="695">
@@ -28936,7 +28936,7 @@
         <v>8</v>
       </c>
       <c r="K695" t="n">
-        <v>1.820700291622185</v>
+        <v>1.818500987688924</v>
       </c>
     </row>
     <row r="696">
@@ -28977,7 +28977,7 @@
         <v>8</v>
       </c>
       <c r="K696" t="n">
-        <v>1.918273620811363</v>
+        <v>1.912349895600684</v>
       </c>
     </row>
     <row r="697">
@@ -29018,7 +29018,7 @@
         <v>8</v>
       </c>
       <c r="K697" t="n">
-        <v>2.085951927987715</v>
+        <v>2.082212319005477</v>
       </c>
     </row>
     <row r="698">
@@ -29059,7 +29059,7 @@
         <v>8</v>
       </c>
       <c r="K698" t="n">
-        <v>2.113660945380497</v>
+        <v>2.111469840299385</v>
       </c>
     </row>
     <row r="699">
@@ -29100,7 +29100,7 @@
         <v>8</v>
       </c>
       <c r="K699" t="n">
-        <v>2.117736224713474</v>
+        <v>2.118854074273631</v>
       </c>
     </row>
     <row r="700">
@@ -29141,7 +29141,7 @@
         <v>8</v>
       </c>
       <c r="K700" t="n">
-        <v>2.101597364922493</v>
+        <v>2.103700220676192</v>
       </c>
     </row>
     <row r="701">
@@ -29182,7 +29182,7 @@
         <v>8</v>
       </c>
       <c r="K701" t="n">
-        <v>2.101597364922493</v>
+        <v>2.103700220676192</v>
       </c>
     </row>
     <row r="702">
@@ -29223,7 +29223,7 @@
         <v>8</v>
       </c>
       <c r="K702" t="n">
-        <v>1.967292061586979</v>
+        <v>1.972843407806867</v>
       </c>
     </row>
     <row r="703">
@@ -29264,7 +29264,7 @@
         <v>8</v>
       </c>
       <c r="K703" t="n">
-        <v>1.909936113265676</v>
+        <v>1.91574956986085</v>
       </c>
     </row>
     <row r="704">
@@ -29305,7 +29305,7 @@
         <v>8</v>
       </c>
       <c r="K704" t="n">
-        <v>1.909936113265676</v>
+        <v>1.91574956986085</v>
       </c>
     </row>
     <row r="705">
@@ -29346,7 +29346,7 @@
         <v>8</v>
       </c>
       <c r="K705" t="n">
-        <v>1.787282127095775</v>
+        <v>1.793788417213851</v>
       </c>
     </row>
     <row r="706">
@@ -29387,7 +29387,7 @@
         <v>8</v>
       </c>
       <c r="K706" t="n">
-        <v>1.73048122868045</v>
+        <v>1.734619354919993</v>
       </c>
     </row>
     <row r="707">
@@ -29428,7 +29428,7 @@
         <v>8</v>
       </c>
       <c r="K707" t="n">
-        <v>1.682560460318243</v>
+        <v>1.688157552425664</v>
       </c>
     </row>
     <row r="708">
@@ -29469,7 +29469,7 @@
         <v>8</v>
       </c>
       <c r="K708" t="n">
-        <v>1.682560460318243</v>
+        <v>1.688157552425664</v>
       </c>
     </row>
     <row r="709">
@@ -29510,7 +29510,7 @@
         <v>8</v>
       </c>
       <c r="K709" t="n">
-        <v>1.618918730535181</v>
+        <v>1.62599535902569</v>
       </c>
     </row>
     <row r="710">
@@ -29551,7 +29551,7 @@
         <v>8</v>
       </c>
       <c r="K710" t="n">
-        <v>1.477629911129343</v>
+        <v>1.487226032433178</v>
       </c>
     </row>
     <row r="711">
@@ -29592,7 +29592,7 @@
         <v>8</v>
       </c>
       <c r="K711" t="n">
-        <v>1.315227967825295</v>
+        <v>1.3219412798284</v>
       </c>
     </row>
     <row r="712">
@@ -29633,7 +29633,7 @@
         <v>8</v>
       </c>
       <c r="K712" t="n">
-        <v>1.251568446319981</v>
+        <v>1.258579706513471</v>
       </c>
     </row>
     <row r="713">
@@ -29674,7 +29674,7 @@
         <v>8</v>
       </c>
       <c r="K713" t="n">
-        <v>1.251568446319981</v>
+        <v>1.258579706513471</v>
       </c>
     </row>
     <row r="714">
@@ -29715,7 +29715,7 @@
         <v>8</v>
       </c>
       <c r="K714" t="n">
-        <v>1.251568446319981</v>
+        <v>1.258579706513471</v>
       </c>
     </row>
     <row r="715">
@@ -29756,7 +29756,7 @@
         <v>8</v>
       </c>
       <c r="K715" t="n">
-        <v>1.147534002383293</v>
+        <v>1.151025321003557</v>
       </c>
     </row>
     <row r="716">
@@ -29797,7 +29797,7 @@
         <v>8</v>
       </c>
       <c r="K716" t="n">
-        <v>1.009690172267892</v>
+        <v>1.012223775959378</v>
       </c>
     </row>
     <row r="717">
@@ -29838,7 +29838,7 @@
         <v>8</v>
       </c>
       <c r="K717" t="n">
-        <v>1.02259655832782</v>
+        <v>1.020925550114743</v>
       </c>
     </row>
     <row r="718">
@@ -29879,7 +29879,7 @@
         <v>8</v>
       </c>
       <c r="K718" t="n">
-        <v>1.063565861714392</v>
+        <v>1.058667749039432</v>
       </c>
     </row>
     <row r="719">
@@ -29920,7 +29920,7 @@
         <v>8</v>
       </c>
       <c r="K719" t="n">
-        <v>1.19278919431808</v>
+        <v>1.180516946321758</v>
       </c>
     </row>
     <row r="720">
@@ -29961,7 +29961,7 @@
         <v>8</v>
       </c>
       <c r="K720" t="n">
-        <v>1.839084754204915</v>
+        <v>1.824551409985406</v>
       </c>
     </row>
     <row r="721">
@@ -30002,7 +30002,7 @@
         <v>8</v>
       </c>
       <c r="K721" t="n">
-        <v>1.839084754204915</v>
+        <v>1.824551409985406</v>
       </c>
     </row>
     <row r="722">
@@ -30043,7 +30043,7 @@
         <v>8</v>
       </c>
       <c r="K722" t="n">
-        <v>1.98262079043228</v>
+        <v>1.983251688918607</v>
       </c>
     </row>
     <row r="723">
@@ -30084,7 +30084,7 @@
         <v>8</v>
       </c>
       <c r="K723" t="n">
-        <v>1.947655842565379</v>
+        <v>1.954308966776333</v>
       </c>
     </row>
     <row r="724">
@@ -30125,7 +30125,7 @@
         <v>8</v>
       </c>
       <c r="K724" t="n">
-        <v>1.947655842565379</v>
+        <v>1.954308966776333</v>
       </c>
     </row>
     <row r="725">
@@ -30166,7 +30166,7 @@
         <v>8</v>
       </c>
       <c r="K725" t="n">
-        <v>1.700512344510753</v>
+        <v>1.705299548520701</v>
       </c>
     </row>
     <row r="726">
@@ -30207,7 +30207,7 @@
         <v>8</v>
       </c>
       <c r="K726" t="n">
-        <v>1.656512115606539</v>
+        <v>1.625451688877914</v>
       </c>
     </row>
     <row r="727">
@@ -30248,7 +30248,7 @@
         <v>8</v>
       </c>
       <c r="K727" t="n">
-        <v>1.622452938042484</v>
+        <v>1.625451688877914</v>
       </c>
     </row>
     <row r="728">
@@ -30289,7 +30289,7 @@
         <v>8</v>
       </c>
       <c r="K728" t="n">
-        <v>1.622452938042484</v>
+        <v>1.625451688877914</v>
       </c>
     </row>
     <row r="729">
@@ -30330,7 +30330,7 @@
         <v>8</v>
       </c>
       <c r="K729" t="n">
-        <v>1.563282564173593</v>
+        <v>1.563638368348338</v>
       </c>
     </row>
     <row r="730">
@@ -30371,7 +30371,7 @@
         <v>8</v>
       </c>
       <c r="K730" t="n">
-        <v>1.693511168302174</v>
+        <v>1.684131467398204</v>
       </c>
     </row>
     <row r="731">
@@ -30412,7 +30412,7 @@
         <v>8</v>
       </c>
       <c r="K731" t="n">
-        <v>1.781893381260321</v>
+        <v>1.772892876800402</v>
       </c>
     </row>
     <row r="732">
@@ -30453,7 +30453,7 @@
         <v>8</v>
       </c>
       <c r="K732" t="n">
-        <v>2.093944313909228</v>
+        <v>2.083541026772862</v>
       </c>
     </row>
     <row r="733">
@@ -30494,7 +30494,7 @@
         <v>8</v>
       </c>
       <c r="K733" t="n">
-        <v>2.182948602558321</v>
+        <v>2.173034162275137</v>
       </c>
     </row>
     <row r="734">
@@ -30535,7 +30535,7 @@
         <v>8</v>
       </c>
       <c r="K734" t="n">
-        <v>2.280893126320981</v>
+        <v>2.2697236528741</v>
       </c>
     </row>
     <row r="735">
@@ -30576,7 +30576,7 @@
         <v>8</v>
       </c>
       <c r="K735" t="n">
-        <v>2.416741306346639</v>
+        <v>2.4145028275097</v>
       </c>
     </row>
     <row r="736">
@@ -30617,7 +30617,7 @@
         <v>8</v>
       </c>
       <c r="K736" t="n">
-        <v>2.415179537402504</v>
+        <v>2.419080255127932</v>
       </c>
     </row>
     <row r="737">
@@ -30658,7 +30658,7 @@
         <v>8</v>
       </c>
       <c r="K737" t="n">
-        <v>2.366265652410208</v>
+        <v>2.372387905631962</v>
       </c>
     </row>
     <row r="738">
@@ -30699,7 +30699,7 @@
         <v>8</v>
       </c>
       <c r="K738" t="n">
-        <v>2.366265652410208</v>
+        <v>2.372387905631962</v>
       </c>
     </row>
     <row r="739">
@@ -30740,7 +30740,7 @@
         <v>8</v>
       </c>
       <c r="K739" t="n">
-        <v>2.366265652410208</v>
+        <v>2.312584701999513</v>
       </c>
     </row>
     <row r="740">
@@ -30781,7 +30781,7 @@
         <v>8</v>
       </c>
       <c r="K740" t="n">
-        <v>2.122573931211128</v>
+        <v>2.125224998483531</v>
       </c>
     </row>
     <row r="741">
@@ -30822,7 +30822,7 @@
         <v>8</v>
       </c>
       <c r="K741" t="n">
-        <v>2.122573931211128</v>
+        <v>2.125224998483531</v>
       </c>
     </row>
     <row r="742">
@@ -30863,7 +30863,7 @@
         <v>8</v>
       </c>
       <c r="K742" t="n">
-        <v>2.122573931211128</v>
+        <v>2.125224998483531</v>
       </c>
     </row>
     <row r="743">
@@ -30904,7 +30904,7 @@
         <v>8</v>
       </c>
       <c r="K743" t="n">
-        <v>2.078343571576254</v>
+        <v>2.079995952326258</v>
       </c>
     </row>
     <row r="744">
@@ -30945,7 +30945,7 @@
         <v>8</v>
       </c>
       <c r="K744" t="n">
-        <v>2.046986122081309</v>
+        <v>2.045884466171625</v>
       </c>
     </row>
     <row r="745">
@@ -30986,7 +30986,7 @@
         <v>8</v>
       </c>
       <c r="K745" t="n">
-        <v>2.046986122081309</v>
+        <v>2.045884466171625</v>
       </c>
     </row>
     <row r="746">
@@ -31027,7 +31027,7 @@
         <v>8</v>
       </c>
       <c r="K746" t="n">
-        <v>2.104211243596873</v>
+        <v>2.098732245966159</v>
       </c>
     </row>
     <row r="747">
@@ -31068,7 +31068,7 @@
         <v>8</v>
       </c>
       <c r="K747" t="n">
-        <v>2.132004279920145</v>
+        <v>2.130836787069494</v>
       </c>
     </row>
     <row r="748">
@@ -31109,7 +31109,7 @@
         <v>8</v>
       </c>
       <c r="K748" t="n">
-        <v>2.132004279920145</v>
+        <v>2.130836787069494</v>
       </c>
     </row>
     <row r="749">
@@ -31150,7 +31150,7 @@
         <v>8</v>
       </c>
       <c r="K749" t="n">
-        <v>2.127043614111169</v>
+        <v>2.112416798550038</v>
       </c>
     </row>
     <row r="750">
@@ -31191,7 +31191,7 @@
         <v>8</v>
       </c>
       <c r="K750" t="n">
-        <v>2.110027818508897</v>
+        <v>2.097153259021341</v>
       </c>
     </row>
     <row r="751">
@@ -31232,7 +31232,7 @@
         <v>8</v>
       </c>
       <c r="K751" t="n">
-        <v>2.096942500799185</v>
+        <v>2.097153259021341</v>
       </c>
     </row>
     <row r="752">
@@ -31273,7 +31273,7 @@
         <v>8</v>
       </c>
       <c r="K752" t="n">
-        <v>2.120316190852739</v>
+        <v>2.12245494623721</v>
       </c>
     </row>
     <row r="753">
@@ -31314,7 +31314,7 @@
         <v>8</v>
       </c>
       <c r="K753" t="n">
-        <v>2.120316190852739</v>
+        <v>2.12245494623721</v>
       </c>
     </row>
     <row r="754">
@@ -31355,7 +31355,7 @@
         <v>8</v>
       </c>
       <c r="K754" t="n">
-        <v>2.088555599819896</v>
+        <v>2.093518993155154</v>
       </c>
     </row>
     <row r="755">
@@ -31396,7 +31396,7 @@
         <v>8</v>
       </c>
       <c r="K755" t="n">
-        <v>2.088555599819896</v>
+        <v>2.093518993155154</v>
       </c>
     </row>
     <row r="756">
@@ -31437,7 +31437,7 @@
         <v>8</v>
       </c>
       <c r="K756" t="n">
-        <v>1.956565276872453</v>
+        <v>1.960099504832889</v>
       </c>
     </row>
     <row r="757">
@@ -31478,7 +31478,7 @@
         <v>8</v>
       </c>
       <c r="K757" t="n">
-        <v>1.956565276872453</v>
+        <v>1.960099504832889</v>
       </c>
     </row>
     <row r="758">
@@ -31519,7 +31519,7 @@
         <v>8</v>
       </c>
       <c r="K758" t="n">
-        <v>1.93634945932227</v>
+        <v>1.937895554251696</v>
       </c>
     </row>
     <row r="759">
@@ -31560,7 +31560,7 @@
         <v>8</v>
       </c>
       <c r="K759" t="n">
-        <v>1.894722325427952</v>
+        <v>1.894009267143002</v>
       </c>
     </row>
     <row r="760">
@@ -31601,7 +31601,7 @@
         <v>8</v>
       </c>
       <c r="K760" t="n">
-        <v>1.894722325427952</v>
+        <v>1.894009267143002</v>
       </c>
     </row>
     <row r="761">
@@ -31642,7 +31642,7 @@
         <v>8</v>
       </c>
       <c r="K761" t="n">
-        <v>1.900347339422678</v>
+        <v>1.899761047338885</v>
       </c>
     </row>
     <row r="762">
@@ -31683,7 +31683,7 @@
         <v>8</v>
       </c>
       <c r="K762" t="n">
-        <v>1.941474758741272</v>
+        <v>1.93729657930629</v>
       </c>
     </row>
     <row r="763">
@@ -31724,7 +31724,7 @@
         <v>8</v>
       </c>
       <c r="K763" t="n">
-        <v>2.152762373911768</v>
+        <v>2.139902174631586</v>
       </c>
     </row>
     <row r="764">
@@ -31765,7 +31765,7 @@
         <v>8</v>
       </c>
       <c r="K764" t="n">
-        <v>2.497634056062145</v>
+        <v>2.484647182069397</v>
       </c>
     </row>
     <row r="765">
@@ -31806,7 +31806,7 @@
         <v>8</v>
       </c>
       <c r="K765" t="n">
-        <v>2.593625708380626</v>
+        <v>2.5830906543961</v>
       </c>
     </row>
     <row r="766">
@@ -31847,7 +31847,7 @@
         <v>8</v>
       </c>
       <c r="K766" t="n">
-        <v>2.666636562112104</v>
+        <v>2.658101052543608</v>
       </c>
     </row>
     <row r="767">
@@ -31888,7 +31888,7 @@
         <v>8</v>
       </c>
       <c r="K767" t="n">
-        <v>2.764471018890406</v>
+        <v>2.787013038201952</v>
       </c>
     </row>
     <row r="768">
@@ -31929,7 +31929,7 @@
         <v>8</v>
       </c>
       <c r="K768" t="n">
-        <v>2.771300942438658</v>
+        <v>2.774688107802824</v>
       </c>
     </row>
     <row r="769">
@@ -31970,7 +31970,7 @@
         <v>8</v>
       </c>
       <c r="K769" t="n">
-        <v>2.771300942438658</v>
+        <v>2.774688107802824</v>
       </c>
     </row>
     <row r="770">
@@ -32011,7 +32011,7 @@
         <v>8</v>
       </c>
       <c r="K770" t="n">
-        <v>2.364027228327107</v>
+        <v>2.378656103011643</v>
       </c>
     </row>
     <row r="771">
@@ -32052,7 +32052,7 @@
         <v>8</v>
       </c>
       <c r="K771" t="n">
-        <v>2.364027228327107</v>
+        <v>2.263860235778804</v>
       </c>
     </row>
     <row r="772">
@@ -32093,7 +32093,7 @@
         <v>8</v>
       </c>
       <c r="K772" t="n">
-        <v>2.120648263833615</v>
+        <v>2.119944119753004</v>
       </c>
     </row>
     <row r="773">
@@ -32134,7 +32134,7 @@
         <v>8</v>
       </c>
       <c r="K773" t="n">
-        <v>2.259724543930963</v>
+        <v>2.253732530808743</v>
       </c>
     </row>
     <row r="774">
@@ -32175,7 +32175,7 @@
         <v>8</v>
       </c>
       <c r="K774" t="n">
-        <v>2.259724543930963</v>
+        <v>2.253732530808743</v>
       </c>
     </row>
     <row r="775">
@@ -32216,7 +32216,7 @@
         <v>8</v>
       </c>
       <c r="K775" t="n">
-        <v>2.259724543930963</v>
+        <v>2.315604536436703</v>
       </c>
     </row>
     <row r="776">
@@ -32257,7 +32257,7 @@
         <v>8</v>
       </c>
       <c r="K776" t="n">
-        <v>2.415821104028975</v>
+        <v>2.41209812454486</v>
       </c>
     </row>
     <row r="777">
@@ -32298,7 +32298,7 @@
         <v>8</v>
       </c>
       <c r="K777" t="n">
-        <v>2.415821104028975</v>
+        <v>2.41209812454486</v>
       </c>
     </row>
     <row r="778">
@@ -32339,7 +32339,7 @@
         <v>8</v>
       </c>
       <c r="K778" t="n">
-        <v>2.415821104028975</v>
+        <v>2.41209812454486</v>
       </c>
     </row>
     <row r="779">
@@ -32380,7 +32380,7 @@
         <v>8</v>
       </c>
       <c r="K779" t="n">
-        <v>2.410542708612877</v>
+        <v>2.414689524136913</v>
       </c>
     </row>
     <row r="780">
@@ -32421,7 +32421,7 @@
         <v>8</v>
       </c>
       <c r="K780" t="n">
-        <v>2.410542708612877</v>
+        <v>2.414689524136913</v>
       </c>
     </row>
     <row r="781">
@@ -32462,7 +32462,7 @@
         <v>8</v>
       </c>
       <c r="K781" t="n">
-        <v>2.37265926837052</v>
+        <v>2.377914018110122</v>
       </c>
     </row>
     <row r="782">
@@ -32503,7 +32503,7 @@
         <v>8</v>
       </c>
       <c r="K782" t="n">
-        <v>2.204836327372331</v>
+        <v>2.213056342382129</v>
       </c>
     </row>
     <row r="783">
@@ -32544,7 +32544,7 @@
         <v>8</v>
       </c>
       <c r="K783" t="n">
-        <v>2.204836327372331</v>
+        <v>2.213056342382129</v>
       </c>
     </row>
     <row r="784">
@@ -32585,7 +32585,7 @@
         <v>8</v>
       </c>
       <c r="K784" t="n">
-        <v>2.144465263635211</v>
+        <v>2.150527035350929</v>
       </c>
     </row>
     <row r="785">
@@ -32626,7 +32626,7 @@
         <v>8</v>
       </c>
       <c r="K785" t="n">
-        <v>2.09911062353117</v>
+        <v>2.105018598563289</v>
       </c>
     </row>
     <row r="786">
@@ -32667,7 +32667,7 @@
         <v>8</v>
       </c>
       <c r="K786" t="n">
-        <v>1.976677679804429</v>
+        <v>1.975385897367746</v>
       </c>
     </row>
     <row r="787">
@@ -32708,7 +32708,7 @@
         <v>8</v>
       </c>
       <c r="K787" t="n">
-        <v>1.996421004461277</v>
+        <v>1.993571797623219</v>
       </c>
     </row>
     <row r="788">
@@ -32749,7 +32749,7 @@
         <v>8</v>
       </c>
       <c r="K788" t="n">
-        <v>2.137860134512813</v>
+        <v>2.130567188412073</v>
       </c>
     </row>
     <row r="789">
@@ -32790,7 +32790,7 @@
         <v>8</v>
       </c>
       <c r="K789" t="n">
-        <v>2.49921810671221</v>
+        <v>2.593646170321894</v>
       </c>
     </row>
     <row r="790">
@@ -32831,7 +32831,7 @@
         <v>8</v>
       </c>
       <c r="K790" t="n">
-        <v>2.49921810671221</v>
+        <v>2.593646170321894</v>
       </c>
     </row>
     <row r="791">
@@ -32872,7 +32872,7 @@
         <v>8</v>
       </c>
       <c r="K791" t="n">
-        <v>2.49921810671221</v>
+        <v>2.593646170321894</v>
       </c>
     </row>
     <row r="792">
@@ -32913,7 +32913,7 @@
         <v>8</v>
       </c>
       <c r="K792" t="n">
-        <v>2.604482546205531</v>
+        <v>2.593646170321894</v>
       </c>
     </row>
     <row r="793">
@@ -32954,7 +32954,7 @@
         <v>8</v>
       </c>
       <c r="K793" t="n">
-        <v>2.844958786193956</v>
+        <v>2.843230618028809</v>
       </c>
     </row>
     <row r="794">
@@ -32995,7 +32995,7 @@
         <v>8</v>
       </c>
       <c r="K794" t="n">
-        <v>2.870933911363835</v>
+        <v>2.868917488639187</v>
       </c>
     </row>
     <row r="795">
@@ -33036,7 +33036,7 @@
         <v>8</v>
       </c>
       <c r="K795" t="n">
-        <v>2.895148439202617</v>
+        <v>2.895338806652064</v>
       </c>
     </row>
     <row r="796">
@@ -33077,7 +33077,7 @@
         <v>8</v>
       </c>
       <c r="K796" t="n">
-        <v>2.67435715442879</v>
+        <v>2.694637611680589</v>
       </c>
     </row>
     <row r="797">
@@ -33118,7 +33118,7 @@
         <v>8</v>
       </c>
       <c r="K797" t="n">
-        <v>2.67435715442879</v>
+        <v>2.694637611680589</v>
       </c>
     </row>
     <row r="798">
@@ -33159,7 +33159,7 @@
         <v>8</v>
       </c>
       <c r="K798" t="n">
-        <v>2.361684273841336</v>
+        <v>2.380110183976558</v>
       </c>
     </row>
     <row r="799">
@@ -33200,7 +33200,7 @@
         <v>8</v>
       </c>
       <c r="K799" t="n">
-        <v>2.177261398182262</v>
+        <v>2.201139425958257</v>
       </c>
     </row>
     <row r="800">
@@ -33241,7 +33241,7 @@
         <v>8</v>
       </c>
       <c r="K800" t="n">
-        <v>1.663202589369392</v>
+        <v>1.677769964737779</v>
       </c>
     </row>
     <row r="801">
@@ -33282,7 +33282,7 @@
         <v>8</v>
       </c>
       <c r="K801" t="n">
-        <v>1.663202589369392</v>
+        <v>1.677769964737779</v>
       </c>
     </row>
     <row r="802">
@@ -33323,7 +33323,7 @@
         <v>8</v>
       </c>
       <c r="K802" t="n">
-        <v>1.663202589369392</v>
+        <v>1.677769964737779</v>
       </c>
     </row>
     <row r="803">
@@ -33364,7 +33364,7 @@
         <v>8</v>
       </c>
       <c r="K803" t="n">
-        <v>1.567066858176465</v>
+        <v>1.574025895310714</v>
       </c>
     </row>
     <row r="804">
@@ -33405,7 +33405,7 @@
         <v>8</v>
       </c>
       <c r="K804" t="n">
-        <v>1.567066858176465</v>
+        <v>1.574025895310714</v>
       </c>
     </row>
     <row r="805">
@@ -33446,7 +33446,7 @@
         <v>8</v>
       </c>
       <c r="K805" t="n">
-        <v>1.494267073931993</v>
+        <v>1.501128647795468</v>
       </c>
     </row>
     <row r="806">
@@ -33487,7 +33487,7 @@
         <v>8</v>
       </c>
       <c r="K806" t="n">
-        <v>1.494267073931993</v>
+        <v>1.501128647795468</v>
       </c>
     </row>
     <row r="807">
@@ -33528,7 +33528,7 @@
         <v>8</v>
       </c>
       <c r="K807" t="n">
-        <v>1.451495013856129</v>
+        <v>1.454909924953208</v>
       </c>
     </row>
     <row r="808">
@@ -33569,7 +33569,7 @@
         <v>8</v>
       </c>
       <c r="K808" t="n">
-        <v>1.494309688327503</v>
+        <v>1.4866923125034</v>
       </c>
     </row>
     <row r="809">
@@ -33610,7 +33610,7 @@
         <v>8</v>
       </c>
       <c r="K809" t="n">
-        <v>1.494309688327503</v>
+        <v>1.4866923125034</v>
       </c>
     </row>
     <row r="810">
@@ -33651,7 +33651,7 @@
         <v>8</v>
       </c>
       <c r="K810" t="n">
-        <v>1.721507861924602</v>
+        <v>1.718626362356324</v>
       </c>
     </row>
     <row r="811">
@@ -33692,7 +33692,7 @@
         <v>8</v>
       </c>
       <c r="K811" t="n">
-        <v>1.811405610871943</v>
+        <v>1.816485748902041</v>
       </c>
     </row>
     <row r="812">
@@ -33733,7 +33733,7 @@
         <v>8</v>
       </c>
       <c r="K812" t="n">
-        <v>1.811405610871943</v>
+        <v>1.816485748902041</v>
       </c>
     </row>
     <row r="813">
@@ -33774,7 +33774,7 @@
         <v>8</v>
       </c>
       <c r="K813" t="n">
-        <v>2.04592629763103</v>
+        <v>2.039099178401283</v>
       </c>
     </row>
     <row r="814">
@@ -33815,7 +33815,7 @@
         <v>8</v>
       </c>
       <c r="K814" t="n">
-        <v>2.04592629763103</v>
+        <v>2.039099178401283</v>
       </c>
     </row>
     <row r="815">
@@ -33856,7 +33856,7 @@
         <v>8</v>
       </c>
       <c r="K815" t="n">
-        <v>2.157864131561417</v>
+        <v>2.143812171822784</v>
       </c>
     </row>
     <row r="816">
@@ -33897,7 +33897,7 @@
         <v>8</v>
       </c>
       <c r="K816" t="n">
-        <v>2.157864131561417</v>
+        <v>2.143812171822784</v>
       </c>
     </row>
     <row r="817">
@@ -33938,7 +33938,7 @@
         <v>8</v>
       </c>
       <c r="K817" t="n">
-        <v>2.33209320171719</v>
+        <v>2.323715375299114</v>
       </c>
     </row>
     <row r="818">
@@ -33979,7 +33979,7 @@
         <v>8</v>
       </c>
       <c r="K818" t="n">
-        <v>2.33209320171719</v>
+        <v>2.323715375299114</v>
       </c>
     </row>
     <row r="819">
@@ -34020,7 +34020,7 @@
         <v>8</v>
       </c>
       <c r="K819" t="n">
-        <v>2.33209320171719</v>
+        <v>2.323715375299114</v>
       </c>
     </row>
     <row r="820">
@@ -34061,7 +34061,7 @@
         <v>8</v>
       </c>
       <c r="K820" t="n">
-        <v>2.33209320171719</v>
+        <v>2.323715375299114</v>
       </c>
     </row>
     <row r="821">
@@ -34102,7 +34102,7 @@
         <v>8</v>
       </c>
       <c r="K821" t="n">
-        <v>2.379908865379889</v>
+        <v>2.372980050715345</v>
       </c>
     </row>
     <row r="822">
@@ -34143,7 +34143,7 @@
         <v>8</v>
       </c>
       <c r="K822" t="n">
-        <v>2.372494968830036</v>
+        <v>2.372980050715345</v>
       </c>
     </row>
     <row r="823">
@@ -34184,7 +34184,7 @@
         <v>8</v>
       </c>
       <c r="K823" t="n">
-        <v>2.388237849791546</v>
+        <v>2.386272191301914</v>
       </c>
     </row>
     <row r="824">
@@ -34225,7 +34225,7 @@
         <v>8</v>
       </c>
       <c r="K824" t="n">
-        <v>2.398397397887693</v>
+        <v>2.410240512030226</v>
       </c>
     </row>
     <row r="825">
@@ -34266,7 +34266,7 @@
         <v>8</v>
       </c>
       <c r="K825" t="n">
-        <v>2.398397397887693</v>
+        <v>2.410240512030226</v>
       </c>
     </row>
     <row r="826">
@@ -34307,7 +34307,7 @@
         <v>8</v>
       </c>
       <c r="K826" t="n">
-        <v>2.410041071849142</v>
+        <v>2.410240512030226</v>
       </c>
     </row>
     <row r="827">
@@ -34348,7 +34348,7 @@
         <v>8</v>
       </c>
       <c r="K827" t="n">
-        <v>2.418781457643176</v>
+        <v>2.424451228169522</v>
       </c>
     </row>
     <row r="828">
@@ -34389,7 +34389,7 @@
         <v>8</v>
       </c>
       <c r="K828" t="n">
-        <v>2.478506544408318</v>
+        <v>2.48830094384646</v>
       </c>
     </row>
     <row r="829">
@@ -34430,7 +34430,7 @@
         <v>8</v>
       </c>
       <c r="K829" t="n">
-        <v>2.430215449802628</v>
+        <v>2.405495944204689</v>
       </c>
     </row>
     <row r="830">
@@ -34471,7 +34471,7 @@
         <v>8</v>
       </c>
       <c r="K830" t="n">
-        <v>2.385614017559097</v>
+        <v>2.385741970699478</v>
       </c>
     </row>
     <row r="831">
@@ -34512,7 +34512,7 @@
         <v>8</v>
       </c>
       <c r="K831" t="n">
-        <v>2.43037306137864</v>
+        <v>2.427764938195817</v>
       </c>
     </row>
     <row r="832">
@@ -34553,7 +34553,7 @@
         <v>8</v>
       </c>
       <c r="K832" t="n">
-        <v>2.462455308958095</v>
+        <v>2.458832659648322</v>
       </c>
     </row>
     <row r="833">
@@ -34594,7 +34594,7 @@
         <v>8</v>
       </c>
       <c r="K833" t="n">
-        <v>2.51663705513572</v>
+        <v>2.518740910122798</v>
       </c>
     </row>
     <row r="834">
@@ -34635,7 +34635,7 @@
         <v>8</v>
       </c>
       <c r="K834" t="n">
-        <v>2.477995397431484</v>
+        <v>2.479394994717921</v>
       </c>
     </row>
     <row r="835">
@@ -34676,7 +34676,7 @@
         <v>8</v>
       </c>
       <c r="K835" t="n">
-        <v>2.466906631060236</v>
+        <v>2.467772604484984</v>
       </c>
     </row>
     <row r="836">
@@ -34717,7 +34717,7 @@
         <v>8</v>
       </c>
       <c r="K836" t="n">
-        <v>2.466223890024045</v>
+        <v>2.465448965894352</v>
       </c>
     </row>
     <row r="837">
@@ -34758,7 +34758,7 @@
         <v>8</v>
       </c>
       <c r="K837" t="n">
-        <v>2.466223890024045</v>
+        <v>2.474555636114062</v>
       </c>
     </row>
     <row r="838">
@@ -34799,7 +34799,7 @@
         <v>8</v>
       </c>
       <c r="K838" t="n">
-        <v>2.475694036284792</v>
+        <v>2.474555636114062</v>
       </c>
     </row>
     <row r="839">
@@ -34840,7 +34840,7 @@
         <v>8</v>
       </c>
       <c r="K839" t="n">
-        <v>2.489148954945082</v>
+        <v>2.487680100158135</v>
       </c>
     </row>
     <row r="840">
@@ -34881,7 +34881,7 @@
         <v>8</v>
       </c>
       <c r="K840" t="n">
-        <v>2.505555608285389</v>
+        <v>2.503725319353638</v>
       </c>
     </row>
     <row r="841">
@@ -34922,7 +34922,7 @@
         <v>8</v>
       </c>
       <c r="K841" t="n">
-        <v>2.518001349977108</v>
+        <v>2.518691392932191</v>
       </c>
     </row>
     <row r="842">
@@ -34963,7 +34963,7 @@
         <v>8</v>
       </c>
       <c r="K842" t="n">
-        <v>2.498740729326588</v>
+        <v>2.501164896954946</v>
       </c>
     </row>
     <row r="843">
@@ -35004,7 +35004,7 @@
         <v>8</v>
       </c>
       <c r="K843" t="n">
-        <v>2.456729766158952</v>
+        <v>2.462039810230236</v>
       </c>
     </row>
     <row r="844">
@@ -35045,7 +35045,7 @@
         <v>8</v>
       </c>
       <c r="K844" t="n">
-        <v>2.395028841717088</v>
+        <v>2.402176286660089</v>
       </c>
     </row>
     <row r="845">
@@ -35086,7 +35086,7 @@
         <v>8</v>
       </c>
       <c r="K845" t="n">
-        <v>2.32079551732591</v>
+        <v>2.327862793824857</v>
       </c>
     </row>
     <row r="846">
@@ -35127,7 +35127,7 @@
         <v>8</v>
       </c>
       <c r="K846" t="n">
-        <v>2.260163915970377</v>
+        <v>2.266179793367706</v>
       </c>
     </row>
     <row r="847">
@@ -35168,7 +35168,7 @@
         <v>8</v>
       </c>
       <c r="K847" t="n">
-        <v>2.260163915970377</v>
+        <v>2.196392617107966</v>
       </c>
     </row>
     <row r="848">
@@ -35209,7 +35209,7 @@
         <v>8</v>
       </c>
       <c r="K848" t="n">
-        <v>1.990513001685938</v>
+        <v>2.000068573965919</v>
       </c>
     </row>
     <row r="849">
@@ -35250,7 +35250,7 @@
         <v>8</v>
       </c>
       <c r="K849" t="n">
-        <v>1.901737332923267</v>
+        <v>1.910565517773104</v>
       </c>
     </row>
     <row r="850">
@@ -35291,7 +35291,7 @@
         <v>8</v>
       </c>
       <c r="K850" t="n">
-        <v>1.901737332923267</v>
+        <v>1.910565517773104</v>
       </c>
     </row>
     <row r="851">
@@ -35332,7 +35332,7 @@
         <v>8</v>
       </c>
       <c r="K851" t="n">
-        <v>1.765386663887886</v>
+        <v>1.762045397402761</v>
       </c>
     </row>
     <row r="852">
@@ -35373,7 +35373,7 @@
         <v>8</v>
       </c>
       <c r="K852" t="n">
-        <v>1.800359690895597</v>
+        <v>1.796604965172823</v>
       </c>
     </row>
     <row r="853">
@@ -35414,7 +35414,7 @@
         <v>8</v>
       </c>
       <c r="K853" t="n">
-        <v>1.800359690895597</v>
+        <v>1.796604965172823</v>
       </c>
     </row>
     <row r="854">
@@ -35455,7 +35455,7 @@
         <v>8</v>
       </c>
       <c r="K854" t="n">
-        <v>1.879853134817324</v>
+        <v>1.874367422663237</v>
       </c>
     </row>
     <row r="855">
@@ -35496,7 +35496,7 @@
         <v>8</v>
       </c>
       <c r="K855" t="n">
-        <v>2.039431485925025</v>
+        <v>2.068854129873861</v>
       </c>
     </row>
     <row r="856">
@@ -35537,7 +35537,7 @@
         <v>8</v>
       </c>
       <c r="K856" t="n">
-        <v>2.071279600648245</v>
+        <v>2.068854129873861</v>
       </c>
     </row>
     <row r="857">
@@ -35578,7 +35578,7 @@
         <v>8</v>
       </c>
       <c r="K857" t="n">
-        <v>2.082864749132923</v>
+        <v>2.09068639638953</v>
       </c>
     </row>
     <row r="858">
@@ -35619,7 +35619,7 @@
         <v>8</v>
       </c>
       <c r="K858" t="n">
-        <v>2.091683866835687</v>
+        <v>2.09068639638953</v>
       </c>
     </row>
     <row r="859">
@@ -35660,7 +35660,7 @@
         <v>8</v>
       </c>
       <c r="K859" t="n">
-        <v>2.101437656464842</v>
+        <v>2.100330540356465</v>
       </c>
     </row>
     <row r="860">
@@ -35701,7 +35701,7 @@
         <v>8</v>
       </c>
       <c r="K860" t="n">
-        <v>2.126210509347888</v>
+        <v>2.139213540298924</v>
       </c>
     </row>
     <row r="861">
@@ -35742,7 +35742,7 @@
         <v>8</v>
       </c>
       <c r="K861" t="n">
-        <v>2.126210509347888</v>
+        <v>2.139213540298924</v>
       </c>
     </row>
     <row r="862">
@@ -35783,7 +35783,7 @@
         <v>8</v>
       </c>
       <c r="K862" t="n">
-        <v>2.158683560646316</v>
+        <v>2.156443764314897</v>
       </c>
     </row>
     <row r="863">
@@ -35824,7 +35824,7 @@
         <v>8</v>
       </c>
       <c r="K863" t="n">
-        <v>2.217953971356496</v>
+        <v>2.213965536316532</v>
       </c>
     </row>
     <row r="864">
@@ -35865,7 +35865,7 @@
         <v>8</v>
       </c>
       <c r="K864" t="n">
-        <v>2.262234459590318</v>
+        <v>2.25621773789748</v>
       </c>
     </row>
     <row r="865">
@@ -35906,7 +35906,7 @@
         <v>8</v>
       </c>
       <c r="K865" t="n">
-        <v>2.442351127658903</v>
+        <v>2.434534846427826</v>
       </c>
     </row>
     <row r="866">
@@ -35947,7 +35947,7 @@
         <v>8</v>
       </c>
       <c r="K866" t="n">
-        <v>2.628243231517054</v>
+        <v>2.615980490246017</v>
       </c>
     </row>
     <row r="867">
@@ -35988,7 +35988,7 @@
         <v>8</v>
       </c>
       <c r="K867" t="n">
-        <v>2.955097713475675</v>
+        <v>2.943591218493609</v>
       </c>
     </row>
     <row r="868">
@@ -36029,7 +36029,7 @@
         <v>8</v>
       </c>
       <c r="K868" t="n">
-        <v>3.183707477943311</v>
+        <v>3.178847798515175</v>
       </c>
     </row>
     <row r="869">
@@ -36070,7 +36070,7 @@
         <v>8</v>
       </c>
       <c r="K869" t="n">
-        <v>3.183707477943311</v>
+        <v>3.178847798515175</v>
       </c>
     </row>
     <row r="870">
@@ -36111,7 +36111,7 @@
         <v>8</v>
       </c>
       <c r="K870" t="n">
-        <v>3.189578177085401</v>
+        <v>3.191860826074765</v>
       </c>
     </row>
     <row r="871">
@@ -36152,7 +36152,7 @@
         <v>8</v>
       </c>
       <c r="K871" t="n">
-        <v>3.123572067069724</v>
+        <v>3.120671217210895</v>
       </c>
     </row>
     <row r="872">
@@ -36193,7 +36193,7 @@
         <v>8</v>
       </c>
       <c r="K872" t="n">
-        <v>3.146114980104624</v>
+        <v>3.152470120737608</v>
       </c>
     </row>
     <row r="873">
@@ -36234,7 +36234,7 @@
         <v>8</v>
       </c>
       <c r="K873" t="n">
-        <v>2.243340984764424</v>
+        <v>2.281019048373247</v>
       </c>
     </row>
     <row r="874">
@@ -36275,7 +36275,7 @@
         <v>8</v>
       </c>
       <c r="K874" t="n">
-        <v>1.930477237662316</v>
+        <v>1.962051103757438</v>
       </c>
     </row>
     <row r="875">
@@ -36316,7 +36316,7 @@
         <v>8</v>
       </c>
       <c r="K875" t="n">
-        <v>1.713091344095494</v>
+        <v>1.735868544426696</v>
       </c>
     </row>
     <row r="876">
@@ -36357,7 +36357,7 @@
         <v>8</v>
       </c>
       <c r="K876" t="n">
-        <v>1.515094718720045</v>
+        <v>1.537605665829464</v>
       </c>
     </row>
     <row r="877">
@@ -36398,7 +36398,7 @@
         <v>8</v>
       </c>
       <c r="K877" t="n">
-        <v>1.165985427964261</v>
+        <v>1.176387638648542</v>
       </c>
     </row>
     <row r="878">
@@ -36439,7 +36439,7 @@
         <v>8</v>
       </c>
       <c r="K878" t="n">
-        <v>1.165985427964261</v>
+        <v>1.176387638648542</v>
       </c>
     </row>
     <row r="879">
@@ -36480,7 +36480,7 @@
         <v>8</v>
       </c>
       <c r="K879" t="n">
-        <v>1.093558568113568</v>
+        <v>1.101303294578668</v>
       </c>
     </row>
     <row r="880">
@@ -36521,7 +36521,7 @@
         <v>8</v>
       </c>
       <c r="K880" t="n">
-        <v>0.9582826037272533</v>
+        <v>0.9926882782088278</v>
       </c>
     </row>
     <row r="881">
@@ -36562,7 +36562,7 @@
         <v>8</v>
       </c>
       <c r="K881" t="n">
-        <v>0.9973577361271827</v>
+        <v>0.9926882782088278</v>
       </c>
     </row>
     <row r="882">
@@ -36603,7 +36603,7 @@
         <v>8</v>
       </c>
       <c r="K882" t="n">
-        <v>1.139453765544397</v>
+        <v>1.131609292761818</v>
       </c>
     </row>
     <row r="883">
@@ -36644,7 +36644,7 @@
         <v>8</v>
       </c>
       <c r="K883" t="n">
-        <v>1.336910185727222</v>
+        <v>1.330616943043011</v>
       </c>
     </row>
     <row r="884">
@@ -36685,7 +36685,7 @@
         <v>8</v>
       </c>
       <c r="K884" t="n">
-        <v>1.436936550939603</v>
+        <v>1.43402139563424</v>
       </c>
     </row>
     <row r="885">
@@ -36726,7 +36726,7 @@
         <v>8</v>
       </c>
       <c r="K885" t="n">
-        <v>1.458835193647743</v>
+        <v>1.456452502868359</v>
       </c>
     </row>
     <row r="886">
@@ -36767,7 +36767,7 @@
         <v>8</v>
       </c>
       <c r="K886" t="n">
-        <v>1.458835193647743</v>
+        <v>1.477396164486504</v>
       </c>
     </row>
     <row r="887">
@@ -36808,7 +36808,7 @@
         <v>8</v>
       </c>
       <c r="K887" t="n">
-        <v>1.514507645168046</v>
+        <v>1.510570654487311</v>
       </c>
     </row>
     <row r="888">
@@ -36849,7 +36849,7 @@
         <v>8</v>
       </c>
       <c r="K888" t="n">
-        <v>1.578082376761902</v>
+        <v>1.574423596533776</v>
       </c>
     </row>
     <row r="889">
@@ -36890,7 +36890,7 @@
         <v>8</v>
       </c>
       <c r="K889" t="n">
-        <v>1.606250864700128</v>
+        <v>1.60333209664648</v>
       </c>
     </row>
     <row r="890">
@@ -36931,7 +36931,7 @@
         <v>8</v>
       </c>
       <c r="K890" t="n">
-        <v>1.690715786828348</v>
+        <v>1.689200879288675</v>
       </c>
     </row>
     <row r="891">
@@ -36972,7 +36972,7 @@
         <v>8</v>
       </c>
       <c r="K891" t="n">
-        <v>1.655594147411692</v>
+        <v>1.65983790731903</v>
       </c>
     </row>
     <row r="892">
@@ -37013,7 +37013,7 @@
         <v>8</v>
       </c>
       <c r="K892" t="n">
-        <v>1.573442696852467</v>
+        <v>1.578001057435892</v>
       </c>
     </row>
     <row r="893">
@@ -37054,7 +37054,7 @@
         <v>8</v>
       </c>
       <c r="K893" t="n">
-        <v>1.573442696852467</v>
+        <v>1.578001057435892</v>
       </c>
     </row>
     <row r="894">
@@ -37095,7 +37095,7 @@
         <v>8</v>
       </c>
       <c r="K894" t="n">
-        <v>1.496089949445877</v>
+        <v>1.493575826130945</v>
       </c>
     </row>
     <row r="895">
@@ -37136,7 +37136,7 @@
         <v>8</v>
       </c>
       <c r="K895" t="n">
-        <v>1.49011956386354</v>
+        <v>1.494497647877825</v>
       </c>
     </row>
     <row r="896">
@@ -37177,7 +37177,7 @@
         <v>8</v>
       </c>
       <c r="K896" t="n">
-        <v>1.496215277623</v>
+        <v>1.494497647877825</v>
       </c>
     </row>
     <row r="897">
@@ -37218,7 +37218,7 @@
         <v>8</v>
       </c>
       <c r="K897" t="n">
-        <v>1.521894968571076</v>
+        <v>1.539779189308738</v>
       </c>
     </row>
     <row r="898">
@@ -37259,7 +37259,7 @@
         <v>8</v>
       </c>
       <c r="K898" t="n">
-        <v>1.542345325814197</v>
+        <v>1.539779189308738</v>
       </c>
     </row>
     <row r="899">
@@ -37300,7 +37300,7 @@
         <v>8</v>
       </c>
       <c r="K899" t="n">
-        <v>1.542345325814197</v>
+        <v>1.56034546583164</v>
       </c>
     </row>
     <row r="900">
@@ -37341,7 +37341,7 @@
         <v>8</v>
       </c>
       <c r="K900" t="n">
-        <v>1.611307907101266</v>
+        <v>1.610765767135665</v>
       </c>
     </row>
     <row r="901">
@@ -37382,7 +37382,7 @@
         <v>8</v>
       </c>
       <c r="K901" t="n">
-        <v>1.611307907101266</v>
+        <v>1.612140267954299</v>
       </c>
     </row>
     <row r="902">
@@ -37423,7 +37423,7 @@
         <v>8</v>
       </c>
       <c r="K902" t="n">
-        <v>1.611701704439107</v>
+        <v>1.612140267954299</v>
       </c>
     </row>
     <row r="903">
@@ -37464,7 +37464,7 @@
         <v>8</v>
       </c>
       <c r="K903" t="n">
-        <v>1.608026536878708</v>
+        <v>1.609073374084381</v>
       </c>
     </row>
     <row r="904">
@@ -37505,7 +37505,7 @@
         <v>8</v>
       </c>
       <c r="K904" t="n">
-        <v>1.608026536878708</v>
+        <v>1.609073374084381</v>
       </c>
     </row>
     <row r="905">
@@ -37546,7 +37546,7 @@
         <v>8</v>
       </c>
       <c r="K905" t="n">
-        <v>1.547132030881837</v>
+        <v>1.559126116035471</v>
       </c>
     </row>
     <row r="906">
@@ -37587,7 +37587,7 @@
         <v>8</v>
       </c>
       <c r="K906" t="n">
-        <v>1.505663368286483</v>
+        <v>1.533058010395774</v>
       </c>
     </row>
     <row r="907">
@@ -37628,7 +37628,7 @@
         <v>8</v>
       </c>
       <c r="K907" t="n">
-        <v>1.505663368286483</v>
+        <v>1.46977170457758</v>
       </c>
     </row>
     <row r="908">
@@ -37669,7 +37669,7 @@
         <v>8</v>
       </c>
       <c r="K908" t="n">
-        <v>1.45935564193908</v>
+        <v>1.46977170457758</v>
       </c>
     </row>
     <row r="909">
@@ -37710,7 +37710,7 @@
         <v>8</v>
       </c>
       <c r="K909" t="n">
-        <v>1.45935564193908</v>
+        <v>1.46977170457758</v>
       </c>
     </row>
     <row r="910">
@@ -37751,7 +37751,7 @@
         <v>8</v>
       </c>
       <c r="K910" t="n">
-        <v>0.1723142853203668</v>
+        <v>0.1980251758672282</v>
       </c>
     </row>
   </sheetData>
